--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3210,27 +3210,180 @@
       </c>
       <c r="N34" s="27" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="n">
+        <v>46257</v>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="inlineStr">
+        <is>
+          <t>1X-GB0W-BY30</t>
+        </is>
+      </c>
+      <c r="H35" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="34" t="n">
+        <v>1122</v>
+      </c>
+      <c r="J35" s="34" t="n">
+        <v>102</v>
+      </c>
+      <c r="K35" s="34" t="n">
+        <v>117</v>
+      </c>
+      <c r="L35" s="34" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M35" s="25" t="inlineStr">
+        <is>
+          <t>249-1251736-6693424</t>
+        </is>
+      </c>
+      <c r="N35" s="27" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G36" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H36" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J36" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K36" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L36" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M36" s="25" t="inlineStr">
+        <is>
+          <t>503-3235803-0999839</t>
+        </is>
+      </c>
+      <c r="N36" s="27" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C37" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H37" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J37" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K37" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L37" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M37" s="25" t="inlineStr">
+        <is>
+          <t>249-4079338-6849421</t>
+        </is>
+      </c>
+      <c r="N37" s="27" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I36" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 37,662</t>
-        </is>
-      </c>
-      <c r="M36" s="32" t="inlineStr">
-        <is>
-          <t>32 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 40,525</t>
+        </is>
+      </c>
+      <c r="M39" s="32" t="inlineStr">
+        <is>
+          <t>35 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
@@ -3396,9 +3549,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3488,7 +3641,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3497,11 +3650,11 @@
         <v>46247</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -3511,25 +3664,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.08</v>
+        <v>6.67</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46255.43991898148</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46249</v>
+        <v>46254</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -3543,29 +3696,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.67</v>
+        <v>6.08</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46255.43991898148</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3794,7 @@
         </is>
       </c>
       <c r="D9" s="32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
@@ -5186,32 +5339,32 @@
       </c>
       <c r="B30" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>503-3235803-0999839</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F30" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H30" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
@@ -5220,32 +5373,32 @@
       </c>
       <c r="B31" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>249-4079338-6849421</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E31" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F31" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H31" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
@@ -5259,7 +5412,7 @@
       </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
@@ -5288,32 +5441,32 @@
       </c>
       <c r="B33" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H33" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -5322,12 +5475,12 @@
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>250-3896584-8818260</t>
+          <t>250-1884634-9513463</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -5344,29 +5497,128 @@
         <v>1</v>
       </c>
       <c r="G34" s="29" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="H34" s="34" t="n">
         <v>1673</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>3316979100148008960</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>249-9105063-4908645</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H35" s="34" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>3316979100148008960</t>
+        </is>
+      </c>
+      <c r="C36" s="36" t="inlineStr">
+        <is>
+          <t>249-1251736-6693424</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="F36" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="29" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="H36" s="34" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>250-3896584-8818260</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G36" s="31" t="n">
-        <v>185.46</v>
-      </c>
-      <c r="H36" s="35" t="n">
-        <v>37662</v>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
+      <c r="G39" s="31" t="n">
+        <v>201.39</v>
+      </c>
+      <c r="H39" s="35" t="n">
+        <v>40525</v>
+      </c>
+    </row>
     <row r="40"/>
     <row r="41"/>
     <row r="42"/>
@@ -5532,7 +5784,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5590,16 +5842,22 @@
     <hyperlink ref="C28" location="'📤销售表'!A32" display="503-8642770-5227060"/>
     <hyperlink ref="B29" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C29" location="'📤销售表'!A34" display="249-9065958-6465408"/>
-    <hyperlink ref="B30" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C30" location="'📤销售表'!A28" display="250-3702632-4431839"/>
-    <hyperlink ref="B31" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C31" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B30" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C30" location="'📤销售表'!A36" display="503-3235803-0999839"/>
+    <hyperlink ref="B31" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C31" location="'📤销售表'!A37" display="249-4079338-6849421"/>
     <hyperlink ref="B32" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C32" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B33" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C33" location="'📤销售表'!A26" display="249-9105063-4908645"/>
-    <hyperlink ref="B34" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C34" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="C32" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B33" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C33" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B34" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C34" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B35" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C35" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="B36" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C36" location="'📤销售表'!A35" display="249-1251736-6693424"/>
+    <hyperlink ref="B37" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C37" location="'📤销售表'!A33" display="250-3896584-8818260"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1229,23 +1229,64 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>多功能清洁棉海绵吸水海绵</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>4個セット(黄色2+灰色2)</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="27" t="inlineStr">
+        <is>
+          <t>3316818973003008960</t>
+        </is>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="27" t="inlineStr">
+        <is>
+          <t>4个套装(黄色2+灰色2) 按1个库存单位计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G15" s="31" t="n">
-        <v>242.5</v>
-      </c>
-      <c r="H15" s="32" t="inlineStr">
-        <is>
-          <t>11 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="G16" s="31" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>12 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="17"/>
     <row r="18"/>
     <row r="19"/>
@@ -1434,9 +1475,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1456,7 +1497,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -3366,25 +3407,76 @@
       </c>
       <c r="N37" s="27" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>多功能清洁棉海绵吸水海绵</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>4個セット</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>HL-LUCS-000X</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="34" t="n">
+        <v>1006</v>
+      </c>
+      <c r="J38" s="34" t="n">
+        <v>92</v>
+      </c>
+      <c r="K38" s="34" t="n">
+        <v>216</v>
+      </c>
+      <c r="L38" s="34" t="n">
+        <v>1189</v>
+      </c>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>503-1271944-7392630</t>
+        </is>
+      </c>
+      <c r="N38" s="27" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 40,525</t>
-        </is>
-      </c>
-      <c r="M39" s="32" t="inlineStr">
-        <is>
-          <t>35 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 41,714</t>
+        </is>
+      </c>
+      <c r="M40" s="32" t="inlineStr">
+        <is>
+          <t>36 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="41"/>
     <row r="42"/>
     <row r="43"/>
@@ -3549,9 +3641,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="I40:L40"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3786,23 +3878,54 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="30" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>多功能清洁棉海绵吸水海绵</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>4個セット(黄色2+灰色2)</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H8" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D10" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t>5 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>6 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13"/>
@@ -3997,8 +4120,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:H10"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4360,7 +4483,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -5605,21 +5728,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t>3316818973003008960</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>503-1271944-7392630</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>多功能清洁棉海绵吸水海绵</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>4個セット</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G39" s="31" t="n">
-        <v>201.39</v>
-      </c>
-      <c r="H39" s="35" t="n">
-        <v>40525</v>
-      </c>
-    </row>
-    <row r="40"/>
+      <c r="G40" s="31" t="n">
+        <v>205.39</v>
+      </c>
+      <c r="H40" s="35" t="n">
+        <v>41714</v>
+      </c>
+    </row>
     <row r="41"/>
     <row r="42"/>
     <row r="43"/>
@@ -5784,7 +5940,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -5858,6 +6014,8 @@
     <hyperlink ref="C36" location="'📤销售表'!A35" display="249-1251736-6693424"/>
     <hyperlink ref="B37" location="'📥进货表'!A13" display="3316801045105008960"/>
     <hyperlink ref="C37" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="B38" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C38" location="'📤销售表'!A38" display="503-1271944-7392630"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3459,25 +3459,76 @@
       </c>
       <c r="N38" s="27" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H39" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J39" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K39" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L39" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M39" s="25" t="inlineStr">
+        <is>
+          <t>503-0624160-6104610</t>
+        </is>
+      </c>
+      <c r="N39" s="27" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I40" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 41,714</t>
-        </is>
-      </c>
-      <c r="M40" s="32" t="inlineStr">
-        <is>
-          <t>36 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 42,643</t>
+        </is>
+      </c>
+      <c r="M41" s="32" t="inlineStr">
+        <is>
+          <t>37 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="42"/>
     <row r="43"/>
     <row r="44"/>
@@ -3641,9 +3692,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3733,7 +3784,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.62</v>
@@ -3746,7 +3797,7 @@
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3969,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -5530,32 +5581,32 @@
       </c>
       <c r="B32" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>503-0624160-6104610</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F32" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H32" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
@@ -5569,7 +5620,7 @@
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
@@ -5603,7 +5654,7 @@
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
@@ -5632,32 +5683,32 @@
       </c>
       <c r="B35" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-1884634-9513463</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H35" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -5671,7 +5722,7 @@
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>249-1251736-6693424</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -5700,32 +5751,32 @@
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>250-3896584-8818260</t>
+          <t>249-1251736-6693424</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="29" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H37" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
@@ -5734,49 +5785,82 @@
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="C38" s="36" t="inlineStr">
+        <is>
+          <t>250-3896584-8818260</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="25" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
           <t>3316818973003008960</t>
         </is>
       </c>
-      <c r="C38" s="36" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>503-1271944-7392630</t>
         </is>
       </c>
-      <c r="D38" s="27" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
         <is>
           <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>4個セット</t>
         </is>
       </c>
-      <c r="F38" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="29" t="n">
+      <c r="F39" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="34" t="n">
+      <c r="H39" s="34" t="n">
         <v>1189</v>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="40"/>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G40" s="31" t="n">
-        <v>205.39</v>
-      </c>
-      <c r="H40" s="35" t="n">
-        <v>41714</v>
-      </c>
-    </row>
-    <row r="41"/>
+      <c r="G41" s="31" t="n">
+        <v>210.27</v>
+      </c>
+      <c r="H41" s="35" t="n">
+        <v>42643</v>
+      </c>
+    </row>
     <row r="42"/>
     <row r="43"/>
     <row r="44"/>
@@ -5940,7 +6024,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6002,20 +6086,22 @@
     <hyperlink ref="C30" location="'📤销售表'!A36" display="503-3235803-0999839"/>
     <hyperlink ref="B31" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C31" location="'📤销售表'!A37" display="249-4079338-6849421"/>
-    <hyperlink ref="B32" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C32" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B32" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C32" location="'📤销售表'!A39" display="503-0624160-6104610"/>
     <hyperlink ref="B33" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C33" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="C33" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B34" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C34" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B35" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C35" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="C34" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B35" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C35" location="'📤销售表'!A30" display="250-1884634-9513463"/>
     <hyperlink ref="B36" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C36" location="'📤销售表'!A35" display="249-1251736-6693424"/>
-    <hyperlink ref="B37" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C37" location="'📤销售表'!A33" display="250-3896584-8818260"/>
-    <hyperlink ref="B38" location="'📥进货表'!A14" display="3316818973003008960"/>
-    <hyperlink ref="C38" location="'📤销售表'!A38" display="503-1271944-7392630"/>
+    <hyperlink ref="C36" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="B37" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C37" location="'📤销售表'!A35" display="249-1251736-6693424"/>
+    <hyperlink ref="B38" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C38" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="B39" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C39" location="'📤销售表'!A38" display="503-1271944-7392630"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1271,23 +1271,64 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>46262.34563657407</v>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX塑料除黄剂</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>100ml+毛巾</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>75.37</v>
+      </c>
+      <c r="H15" s="27" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>除黄剂补货10个</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G16" s="31" t="n">
-        <v>246.5</v>
-      </c>
-      <c r="H16" s="32" t="inlineStr">
-        <is>
-          <t>12 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="G17" s="31" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>13 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
@@ -1475,9 +1516,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3511,27 +3552,180 @@
       </c>
       <c r="N39" s="27" t="n"/>
     </row>
-    <row r="40"/>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H40" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J40" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K40" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L40" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M40" s="25" t="inlineStr">
+        <is>
+          <t>249-3155796-5912651</t>
+        </is>
+      </c>
+      <c r="N40" s="27" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G41" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H41" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J41" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K41" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L41" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M41" s="25" t="inlineStr">
+        <is>
+          <t>249-0736245-4273400</t>
+        </is>
+      </c>
+      <c r="N41" s="27" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D42" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G42" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H42" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="34" t="n">
+        <v>2936</v>
+      </c>
+      <c r="J42" s="34" t="n">
+        <v>266</v>
+      </c>
+      <c r="K42" s="34" t="n">
+        <v>388</v>
+      </c>
+      <c r="L42" s="34" t="n">
+        <v>3346</v>
+      </c>
+      <c r="M42" s="25" t="inlineStr">
+        <is>
+          <t>503-8823986-1859812</t>
+        </is>
+      </c>
+      <c r="N42" s="27" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I41" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 42,643</t>
-        </is>
-      </c>
-      <c r="M41" s="32" t="inlineStr">
-        <is>
-          <t>37 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 49,335</t>
+        </is>
+      </c>
+      <c r="M44" s="32" t="inlineStr">
+        <is>
+          <t>40 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="45"/>
     <row r="46"/>
     <row r="47"/>
@@ -3692,9 +3886,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="A44:D44"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3775,29 +3969,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.62</v>
+        <v>7.12</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46247</v>
+        <v>46262.34563657407</v>
       </c>
       <c r="G3" s="33" t="n">
         <v>46261</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -3807,25 +4001,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.67</v>
+        <v>4.62</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46255.43991898148</v>
+        <v>46247</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -3969,7 +4163,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -5819,51 +6013,150 @@
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>249-3155796-5912651</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="25" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="36" t="inlineStr">
+        <is>
+          <t>3316801045105008960</t>
+        </is>
+      </c>
+      <c r="C40" s="36" t="inlineStr">
+        <is>
+          <t>249-0736245-4273400</t>
+        </is>
+      </c>
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F40" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="25" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="36" t="inlineStr">
+        <is>
           <t>3316818973003008960</t>
         </is>
       </c>
-      <c r="C39" s="36" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>503-1271944-7392630</t>
         </is>
       </c>
-      <c r="D39" s="27" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
-      <c r="E39" s="27" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>4個セット</t>
         </is>
       </c>
-      <c r="F39" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="29" t="n">
+      <c r="F41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="34" t="n">
+      <c r="H41" s="34" t="n">
         <v>1189</v>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="25" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C42" s="36" t="inlineStr">
+        <is>
+          <t>503-8823986-1859812</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F42" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="29" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="H42" s="34" t="n">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G41" s="31" t="n">
-        <v>210.27</v>
-      </c>
-      <c r="H41" s="35" t="n">
-        <v>42643</v>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
+      <c r="G44" s="31" t="n">
+        <v>239.34</v>
+      </c>
+      <c r="H44" s="35" t="n">
+        <v>49335</v>
+      </c>
+    </row>
     <row r="45"/>
     <row r="46"/>
     <row r="47"/>
@@ -6024,7 +6317,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6100,8 +6393,14 @@
     <hyperlink ref="C37" location="'📤销售表'!A35" display="249-1251736-6693424"/>
     <hyperlink ref="B38" location="'📥进货表'!A13" display="3316801045105008960"/>
     <hyperlink ref="C38" location="'📤销售表'!A33" display="250-3896584-8818260"/>
-    <hyperlink ref="B39" location="'📥进货表'!A14" display="3316818973003008960"/>
-    <hyperlink ref="C39" location="'📤销售表'!A38" display="503-1271944-7392630"/>
+    <hyperlink ref="B39" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C39" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="B40" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C40" location="'📤销售表'!A41" display="249-0736245-4273400"/>
+    <hyperlink ref="B41" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C41" location="'📤销售表'!A38" display="503-1271944-7392630"/>
+    <hyperlink ref="B42" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C42" location="'📤销售表'!A42" display="503-8823986-1859812"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3708,26 +3708,128 @@
       </c>
       <c r="N42" s="27" t="n"/>
     </row>
-    <row r="43"/>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C43" s="33" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D43" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F43" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J43" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K43" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L43" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M43" s="25" t="inlineStr">
+        <is>
+          <t>503-9622492-9545465</t>
+        </is>
+      </c>
+      <c r="N43" s="27" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J44" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K44" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L44" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M44" s="25" t="inlineStr">
+        <is>
+          <t>249-4753098-4602218</t>
+        </is>
+      </c>
+      <c r="N44" s="27" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I44" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 49,335</t>
-        </is>
-      </c>
-      <c r="M44" s="32" t="inlineStr">
-        <is>
-          <t>40 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46"/>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 52,681</t>
+        </is>
+      </c>
+      <c r="M46" s="32" t="inlineStr">
+        <is>
+          <t>42 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="47"/>
     <row r="48"/>
     <row r="49"/>
@@ -3886,9 +3988,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="I46:L46"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3978,7 +4080,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>7.12</v>
@@ -3987,11 +4089,11 @@
         <v>46262.34563657407</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (8个)</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4265,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -6143,22 +6245,88 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="25" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>503-9622492-9545465</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H43" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="25" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C44" s="36" t="inlineStr">
+        <is>
+          <t>249-4753098-4602218</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H44" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G44" s="31" t="n">
-        <v>239.34</v>
-      </c>
-      <c r="H44" s="35" t="n">
-        <v>49335</v>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46"/>
+      <c r="G46" s="31" t="n">
+        <v>254.42</v>
+      </c>
+      <c r="H46" s="35" t="n">
+        <v>52681</v>
+      </c>
+    </row>
     <row r="47"/>
     <row r="48"/>
     <row r="49"/>
@@ -6317,7 +6485,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A46:E46"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6401,6 +6569,10 @@
     <hyperlink ref="C41" location="'📤销售表'!A38" display="503-1271944-7392630"/>
     <hyperlink ref="B42" location="'📥进货表'!A15" display="3316818145041008960"/>
     <hyperlink ref="C42" location="'📤销售表'!A42" display="503-8823986-1859812"/>
+    <hyperlink ref="B43" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C43" location="'📤销售表'!A43" display="503-9622492-9545465"/>
+    <hyperlink ref="B44" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C44" location="'📤销售表'!A44" display="249-4753098-4602218"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3812,27 +3812,180 @@
       </c>
       <c r="N44" s="27" t="n"/>
     </row>
-    <row r="45"/>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F45" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H45" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J45" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K45" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L45" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M45" s="25" t="inlineStr">
+        <is>
+          <t>503-0662665-5424655</t>
+        </is>
+      </c>
+      <c r="N45" s="27" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H46" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J46" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K46" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L46" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M46" s="25" t="inlineStr">
+        <is>
+          <t>249-2270812-8468652</t>
+        </is>
+      </c>
+      <c r="N46" s="27" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D47" s="33" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F47" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G47" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H47" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J47" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K47" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L47" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M47" s="25" t="inlineStr">
+        <is>
+          <t>249-6190540-1277415</t>
+        </is>
+      </c>
+      <c r="N47" s="27" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I46" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 52,681</t>
-        </is>
-      </c>
-      <c r="M46" s="32" t="inlineStr">
-        <is>
-          <t>42 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+      <c r="I49" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 56,212</t>
+        </is>
+      </c>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>45 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
@@ -3988,9 +4141,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4080,7 +4233,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>7.12</v>
@@ -4089,11 +4242,11 @@
         <v>46262.34563657407</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -4103,29 +4256,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>4.62</v>
+        <v>6.08</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46247</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46261</v>
+        <v>46257</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -4135,29 +4288,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46257</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -4167,25 +4320,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -4199,25 +4352,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>20</v>
+        <v>4.62</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46247</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46221</v>
+        <v>46266</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -4265,7 +4418,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -5911,32 +6064,32 @@
       </c>
       <c r="B33" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>503-0662665-5424655</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F33" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H33" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
@@ -5945,32 +6098,32 @@
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>249-2270812-8468652</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F34" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H34" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -5984,7 +6137,7 @@
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
@@ -6013,32 +6166,32 @@
       </c>
       <c r="B36" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F36" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H36" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
@@ -6047,32 +6200,32 @@
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>249-1251736-6693424</t>
+          <t>250-1884634-9513463</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F37" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H37" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
@@ -6081,32 +6234,32 @@
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C38" s="36" t="inlineStr">
         <is>
-          <t>250-3896584-8818260</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="29" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H38" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
@@ -6115,32 +6268,32 @@
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>249-3155796-5912651</t>
+          <t>249-1251736-6693424</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E39" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F39" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G39" s="29" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H39" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
@@ -6154,7 +6307,7 @@
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>249-0736245-4273400</t>
+          <t>250-3896584-8818260</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -6183,32 +6336,32 @@
       </c>
       <c r="B41" s="36" t="inlineStr">
         <is>
-          <t>3316818973003008960</t>
+          <t>3316801045105008960</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>503-1271944-7392630</t>
+          <t>249-3155796-5912651</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>4個セット</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H41" s="34" t="n">
-        <v>1189</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
@@ -6217,12 +6370,12 @@
       </c>
       <c r="B42" s="36" t="inlineStr">
         <is>
-          <t>3316818145041008960</t>
+          <t>3316801045105008960</t>
         </is>
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>503-8823986-1859812</t>
+          <t>249-0736245-4273400</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -6236,13 +6389,13 @@
         </is>
       </c>
       <c r="F42" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="29" t="n">
-        <v>15.07</v>
+        <v>7</v>
       </c>
       <c r="H42" s="34" t="n">
-        <v>3346</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
@@ -6251,32 +6404,32 @@
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>3316818145041008960</t>
+          <t>3316818973003008960</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>503-9622492-9545465</t>
+          <t>503-1271944-7392630</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>4個セット</t>
         </is>
       </c>
       <c r="F43" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="29" t="n">
-        <v>7.54</v>
+        <v>4</v>
       </c>
       <c r="H43" s="34" t="n">
-        <v>1673</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
@@ -6290,46 +6443,145 @@
       </c>
       <c r="C44" s="36" t="inlineStr">
         <is>
+          <t>503-8823986-1859812</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F44" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="29" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="H44" s="34" t="n">
+        <v>3346</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="25" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>503-9622492-9545465</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H45" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="25" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C46" s="36" t="inlineStr">
+        <is>
           <t>249-4753098-4602218</t>
         </is>
       </c>
-      <c r="D44" s="27" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
         <is>
           <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
-      <c r="E44" s="27" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="F44" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="29" t="n">
+      <c r="F46" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="29" t="n">
         <v>7.54</v>
       </c>
-      <c r="H44" s="34" t="n">
+      <c r="H46" s="34" t="n">
         <v>1673</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="25" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>249-6190540-1277415</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H47" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G46" s="31" t="n">
-        <v>254.42</v>
-      </c>
-      <c r="H46" s="35" t="n">
-        <v>52681</v>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
+      <c r="G49" s="31" t="n">
+        <v>271.72</v>
+      </c>
+      <c r="H49" s="35" t="n">
+        <v>56212</v>
+      </c>
+    </row>
     <row r="50"/>
     <row r="51"/>
     <row r="52"/>
@@ -6485,7 +6737,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6549,30 +6801,36 @@
     <hyperlink ref="C31" location="'📤销售表'!A37" display="249-4079338-6849421"/>
     <hyperlink ref="B32" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C32" location="'📤销售表'!A39" display="503-0624160-6104610"/>
-    <hyperlink ref="B33" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C33" location="'📤销售表'!A28" display="250-3702632-4431839"/>
-    <hyperlink ref="B34" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C34" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B33" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C33" location="'📤销售表'!A45" display="503-0662665-5424655"/>
+    <hyperlink ref="B34" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C34" location="'📤销售表'!A46" display="249-2270812-8468652"/>
     <hyperlink ref="B35" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C35" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B36" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C36" location="'📤销售表'!A26" display="249-9105063-4908645"/>
-    <hyperlink ref="B37" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C37" location="'📤销售表'!A35" display="249-1251736-6693424"/>
-    <hyperlink ref="B38" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C38" location="'📤销售表'!A33" display="250-3896584-8818260"/>
-    <hyperlink ref="B39" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C39" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="C35" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B36" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C36" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B37" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C37" location="'📤销售表'!A30" display="250-1884634-9513463"/>
+    <hyperlink ref="B38" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C38" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="B39" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C39" location="'📤销售表'!A35" display="249-1251736-6693424"/>
     <hyperlink ref="B40" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C40" location="'📤销售表'!A41" display="249-0736245-4273400"/>
-    <hyperlink ref="B41" location="'📥进货表'!A14" display="3316818973003008960"/>
-    <hyperlink ref="C41" location="'📤销售表'!A38" display="503-1271944-7392630"/>
-    <hyperlink ref="B42" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C42" location="'📤销售表'!A42" display="503-8823986-1859812"/>
-    <hyperlink ref="B43" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C43" location="'📤销售表'!A43" display="503-9622492-9545465"/>
+    <hyperlink ref="C40" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="B41" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C41" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="B42" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C42" location="'📤销售表'!A41" display="249-0736245-4273400"/>
+    <hyperlink ref="B43" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C43" location="'📤销售表'!A38" display="503-1271944-7392630"/>
     <hyperlink ref="B44" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C44" location="'📤销售表'!A44" display="249-4753098-4602218"/>
+    <hyperlink ref="C44" location="'📤销售表'!A42" display="503-8823986-1859812"/>
+    <hyperlink ref="B45" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C45" location="'📤销售表'!A43" display="503-9622492-9545465"/>
+    <hyperlink ref="B46" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C46" location="'📤销售表'!A44" display="249-4753098-4602218"/>
+    <hyperlink ref="B47" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C47" location="'📤销售表'!A47" display="249-6190540-1277415"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -3968,26 +3968,128 @@
       </c>
       <c r="N47" s="27" t="n"/>
     </row>
-    <row r="48"/>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D48" s="33" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G48" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H48" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J48" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K48" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L48" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M48" s="25" t="inlineStr">
+        <is>
+          <t>250-4684901-9947011</t>
+        </is>
+      </c>
+      <c r="N48" s="27" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="n">
+        <v>46268</v>
+      </c>
+      <c r="D49" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>1X-GB0W-BY30</t>
+        </is>
+      </c>
+      <c r="H49" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="34" t="n">
+        <v>1122</v>
+      </c>
+      <c r="J49" s="34" t="n">
+        <v>102</v>
+      </c>
+      <c r="K49" s="34" t="n">
+        <v>117</v>
+      </c>
+      <c r="L49" s="34" t="n">
+        <v>1005</v>
+      </c>
+      <c r="M49" s="25" t="inlineStr">
+        <is>
+          <t>250-4415779-1797458</t>
+        </is>
+      </c>
+      <c r="N49" s="27" t="n"/>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I49" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 56,212</t>
-        </is>
-      </c>
-      <c r="M49" s="32" t="inlineStr">
-        <is>
-          <t>45 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
+      <c r="I51" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 58,890</t>
+        </is>
+      </c>
+      <c r="M51" s="32" t="inlineStr">
+        <is>
+          <t>47 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="52"/>
     <row r="53"/>
     <row r="54"/>
@@ -4141,9 +4243,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A51:D51"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4233,7 +4335,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>7.12</v>
@@ -4242,11 +4344,11 @@
         <v>46262.34563657407</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (4个)</t>
         </is>
       </c>
     </row>
@@ -4256,29 +4358,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46257</v>
+        <v>46214</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -4288,25 +4390,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -4320,25 +4422,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>6.08</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46268</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -4418,7 +4520,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -6302,32 +6404,32 @@
       </c>
       <c r="B40" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>250-3896584-8818260</t>
+          <t>250-4415779-1797458</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F40" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="29" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H40" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
@@ -6341,7 +6443,7 @@
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>249-3155796-5912651</t>
+          <t>250-3896584-8818260</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
@@ -6375,7 +6477,7 @@
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>249-0736245-4273400</t>
+          <t>249-3155796-5912651</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -6404,32 +6506,32 @@
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>3316818973003008960</t>
+          <t>3316801045105008960</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>503-1271944-7392630</t>
+          <t>249-0736245-4273400</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E43" s="27" t="inlineStr">
         <is>
-          <t>4個セット</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F43" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" s="34" t="n">
-        <v>1189</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
@@ -6438,32 +6540,32 @@
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
-          <t>3316818145041008960</t>
+          <t>3316818973003008960</t>
         </is>
       </c>
       <c r="C44" s="36" t="inlineStr">
         <is>
-          <t>503-8823986-1859812</t>
+          <t>503-1271944-7392630</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>4個セット</t>
         </is>
       </c>
       <c r="F44" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="29" t="n">
-        <v>15.07</v>
+        <v>4</v>
       </c>
       <c r="H44" s="34" t="n">
-        <v>3346</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
@@ -6477,7 +6579,7 @@
       </c>
       <c r="C45" s="36" t="inlineStr">
         <is>
-          <t>503-9622492-9545465</t>
+          <t>503-8823986-1859812</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
@@ -6491,13 +6593,13 @@
         </is>
       </c>
       <c r="F45" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>7.54</v>
+        <v>15.07</v>
       </c>
       <c r="H45" s="34" t="n">
-        <v>1673</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
@@ -6511,7 +6613,7 @@
       </c>
       <c r="C46" s="36" t="inlineStr">
         <is>
-          <t>249-4753098-4602218</t>
+          <t>503-9622492-9545465</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -6545,7 +6647,7 @@
       </c>
       <c r="C47" s="36" t="inlineStr">
         <is>
-          <t>249-6190540-1277415</t>
+          <t>249-4753098-4602218</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -6568,22 +6670,88 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="25" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C48" s="36" t="inlineStr">
+        <is>
+          <t>249-6190540-1277415</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F48" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H48" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>250-4684901-9947011</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F49" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H49" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G49" s="31" t="n">
-        <v>271.72</v>
-      </c>
-      <c r="H49" s="35" t="n">
-        <v>56212</v>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
+      <c r="G51" s="31" t="n">
+        <v>285.43</v>
+      </c>
+      <c r="H51" s="35" t="n">
+        <v>58890</v>
+      </c>
+    </row>
     <row r="52"/>
     <row r="53"/>
     <row r="54"/>
@@ -6737,7 +6905,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6815,22 +6983,26 @@
     <hyperlink ref="C38" location="'📤销售表'!A26" display="249-9105063-4908645"/>
     <hyperlink ref="B39" location="'📥进货表'!A12" display="3316979100148008960"/>
     <hyperlink ref="C39" location="'📤销售表'!A35" display="249-1251736-6693424"/>
-    <hyperlink ref="B40" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C40" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="B40" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C40" location="'📤销售表'!A49" display="250-4415779-1797458"/>
     <hyperlink ref="B41" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C41" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="C41" location="'📤销售表'!A33" display="250-3896584-8818260"/>
     <hyperlink ref="B42" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C42" location="'📤销售表'!A41" display="249-0736245-4273400"/>
-    <hyperlink ref="B43" location="'📥进货表'!A14" display="3316818973003008960"/>
-    <hyperlink ref="C43" location="'📤销售表'!A38" display="503-1271944-7392630"/>
-    <hyperlink ref="B44" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C44" location="'📤销售表'!A42" display="503-8823986-1859812"/>
+    <hyperlink ref="C42" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="B43" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C43" location="'📤销售表'!A41" display="249-0736245-4273400"/>
+    <hyperlink ref="B44" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C44" location="'📤销售表'!A38" display="503-1271944-7392630"/>
     <hyperlink ref="B45" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C45" location="'📤销售表'!A43" display="503-9622492-9545465"/>
+    <hyperlink ref="C45" location="'📤销售表'!A42" display="503-8823986-1859812"/>
     <hyperlink ref="B46" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C46" location="'📤销售表'!A44" display="249-4753098-4602218"/>
+    <hyperlink ref="C46" location="'📤销售表'!A43" display="503-9622492-9545465"/>
     <hyperlink ref="B47" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C47" location="'📤销售表'!A47" display="249-6190540-1277415"/>
+    <hyperlink ref="C47" location="'📤销售表'!A44" display="249-4753098-4602218"/>
+    <hyperlink ref="B48" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C48" location="'📤销售表'!A47" display="249-6190540-1277415"/>
+    <hyperlink ref="B49" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C49" location="'📤销售表'!A48" display="250-4684901-9947011"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1313,23 +1313,64 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>多功能不锈钢按压式压蒜器</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>按压压蒜器1个 绿色</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="H16" s="27" t="inlineStr">
+        <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="J16" s="27" t="inlineStr">
+        <is>
+          <t>压蒜器补货10个</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G17" s="31" t="n">
-        <v>321.87</v>
-      </c>
-      <c r="H17" s="32" t="inlineStr">
-        <is>
-          <t>13 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="G18" s="31" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>14 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
@@ -1516,9 +1557,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="H18:J18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4072,26 +4113,128 @@
       </c>
       <c r="N49" s="27" t="n"/>
     </row>
-    <row r="50"/>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D50" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H50" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J50" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M50" s="25" t="inlineStr">
+        <is>
+          <t>503-6026474-9279869</t>
+        </is>
+      </c>
+      <c r="N50" s="27" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C51" s="33" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D51" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G51" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H51" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J51" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K51" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L51" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M51" s="25" t="inlineStr">
+        <is>
+          <t>249-7820833-4454235</t>
+        </is>
+      </c>
+      <c r="N51" s="27" t="n"/>
+    </row>
+    <row r="52"/>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I51" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 58,890</t>
-        </is>
-      </c>
-      <c r="M51" s="32" t="inlineStr">
-        <is>
-          <t>47 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
+      <c r="I53" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 60,748</t>
+        </is>
+      </c>
+      <c r="M53" s="32" t="inlineStr">
+        <is>
+          <t>49 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
@@ -4243,9 +4386,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="M53:N53"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4326,29 +4469,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>7.12</v>
+        <v>4.61</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46262.34563657407</v>
+        <v>46270</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (4个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -4358,29 +4501,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>7.12</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46262.34563657407</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46214</v>
+        <v>46267</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (4个)</t>
         </is>
       </c>
     </row>
@@ -4390,25 +4533,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -4422,25 +4565,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>6.08</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46268</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -4454,25 +4597,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>4.62</v>
+        <v>6.08</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46247</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -4520,7 +4663,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -6234,32 +6377,32 @@
       </c>
       <c r="B35" s="36" t="inlineStr">
         <is>
-          <t>3316370306219008960</t>
+          <t>331637642022008960</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>250-3702632-4431839</t>
+          <t>503-6026474-9279869</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F35" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="29" t="n">
-        <v>6.33</v>
+        <v>4.88</v>
       </c>
       <c r="H35" s="34" t="n">
-        <v>1673</v>
+        <v>929</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
@@ -6273,7 +6416,7 @@
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>250-9517256-2524664</t>
+          <t>250-3702632-4431839</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
@@ -6307,7 +6450,7 @@
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>250-1884634-9513463</t>
+          <t>250-9517256-2524664</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
@@ -6336,32 +6479,32 @@
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
-          <t>3316979100148008960</t>
+          <t>3316370306219008960</t>
         </is>
       </c>
       <c r="C38" s="36" t="inlineStr">
         <is>
-          <t>249-9105063-4908645</t>
+          <t>250-1884634-9513463</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F38" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="29" t="n">
-        <v>6.17</v>
+        <v>6.33</v>
       </c>
       <c r="H38" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
@@ -6375,7 +6518,7 @@
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>249-1251736-6693424</t>
+          <t>249-9105063-4908645</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
@@ -6409,7 +6552,7 @@
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>250-4415779-1797458</t>
+          <t>249-1251736-6693424</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
@@ -6438,32 +6581,32 @@
       </c>
       <c r="B41" s="36" t="inlineStr">
         <is>
-          <t>3316801045105008960</t>
+          <t>3316979100148008960</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>250-3896584-8818260</t>
+          <t>250-4415779-1797458</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F41" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="29" t="n">
-        <v>7</v>
+        <v>6.17</v>
       </c>
       <c r="H41" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
@@ -6477,7 +6620,7 @@
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>249-3155796-5912651</t>
+          <t>250-3896584-8818260</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
@@ -6511,7 +6654,7 @@
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>249-0736245-4273400</t>
+          <t>249-3155796-5912651</t>
         </is>
       </c>
       <c r="D43" s="27" t="inlineStr">
@@ -6540,32 +6683,32 @@
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
-          <t>3316818973003008960</t>
+          <t>3316801045105008960</t>
         </is>
       </c>
       <c r="C44" s="36" t="inlineStr">
         <is>
-          <t>503-1271944-7392630</t>
+          <t>249-0736245-4273400</t>
         </is>
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
-          <t>4個セット</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F44" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H44" s="34" t="n">
-        <v>1189</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
@@ -6574,32 +6717,32 @@
       </c>
       <c r="B45" s="36" t="inlineStr">
         <is>
-          <t>3316818145041008960</t>
+          <t>3316818973003008960</t>
         </is>
       </c>
       <c r="C45" s="36" t="inlineStr">
         <is>
-          <t>503-8823986-1859812</t>
+          <t>503-1271944-7392630</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>4個セット</t>
         </is>
       </c>
       <c r="F45" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>15.07</v>
+        <v>4</v>
       </c>
       <c r="H45" s="34" t="n">
-        <v>3346</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
@@ -6613,7 +6756,7 @@
       </c>
       <c r="C46" s="36" t="inlineStr">
         <is>
-          <t>503-9622492-9545465</t>
+          <t>503-8823986-1859812</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
@@ -6627,13 +6770,13 @@
         </is>
       </c>
       <c r="F46" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="29" t="n">
-        <v>7.54</v>
+        <v>15.07</v>
       </c>
       <c r="H46" s="34" t="n">
-        <v>1673</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
@@ -6647,7 +6790,7 @@
       </c>
       <c r="C47" s="36" t="inlineStr">
         <is>
-          <t>249-4753098-4602218</t>
+          <t>503-9622492-9545465</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
@@ -6681,7 +6824,7 @@
       </c>
       <c r="C48" s="36" t="inlineStr">
         <is>
-          <t>249-6190540-1277415</t>
+          <t>249-4753098-4602218</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
@@ -6715,7 +6858,7 @@
       </c>
       <c r="C49" s="36" t="inlineStr">
         <is>
-          <t>250-4684901-9947011</t>
+          <t>249-6190540-1277415</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
@@ -6738,22 +6881,88 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="36" t="inlineStr">
+        <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>250-4684901-9947011</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F50" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H50" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="25" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="36" t="inlineStr">
+        <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>249-7820833-4454235</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F51" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G51" s="31" t="n">
-        <v>285.43</v>
-      </c>
-      <c r="H51" s="35" t="n">
-        <v>58890</v>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
+      <c r="G53" s="31" t="n">
+        <v>294.89</v>
+      </c>
+      <c r="H53" s="35" t="n">
+        <v>60748</v>
+      </c>
+    </row>
     <row r="54"/>
     <row r="55"/>
     <row r="56"/>
@@ -6905,7 +7114,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6973,36 +7182,40 @@
     <hyperlink ref="C33" location="'📤销售表'!A45" display="503-0662665-5424655"/>
     <hyperlink ref="B34" location="'📥进货表'!A10" display="331637642022008960"/>
     <hyperlink ref="C34" location="'📤销售表'!A46" display="249-2270812-8468652"/>
-    <hyperlink ref="B35" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C35" location="'📤销售表'!A28" display="250-3702632-4431839"/>
+    <hyperlink ref="B35" location="'📥进货表'!A10" display="331637642022008960"/>
+    <hyperlink ref="C35" location="'📤销售表'!A50" display="503-6026474-9279869"/>
     <hyperlink ref="B36" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C36" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="C36" location="'📤销售表'!A28" display="250-3702632-4431839"/>
     <hyperlink ref="B37" location="'📥进货表'!A11" display="3316370306219008960"/>
-    <hyperlink ref="C37" location="'📤销售表'!A30" display="250-1884634-9513463"/>
-    <hyperlink ref="B38" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C38" location="'📤销售表'!A26" display="249-9105063-4908645"/>
+    <hyperlink ref="C37" location="'📤销售表'!A29" display="250-9517256-2524664"/>
+    <hyperlink ref="B38" location="'📥进货表'!A11" display="3316370306219008960"/>
+    <hyperlink ref="C38" location="'📤销售表'!A30" display="250-1884634-9513463"/>
     <hyperlink ref="B39" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C39" location="'📤销售表'!A35" display="249-1251736-6693424"/>
+    <hyperlink ref="C39" location="'📤销售表'!A26" display="249-9105063-4908645"/>
     <hyperlink ref="B40" location="'📥进货表'!A12" display="3316979100148008960"/>
-    <hyperlink ref="C40" location="'📤销售表'!A49" display="250-4415779-1797458"/>
-    <hyperlink ref="B41" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C41" location="'📤销售表'!A33" display="250-3896584-8818260"/>
+    <hyperlink ref="C40" location="'📤销售表'!A35" display="249-1251736-6693424"/>
+    <hyperlink ref="B41" location="'📥进货表'!A12" display="3316979100148008960"/>
+    <hyperlink ref="C41" location="'📤销售表'!A49" display="250-4415779-1797458"/>
     <hyperlink ref="B42" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C42" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="C42" location="'📤销售表'!A33" display="250-3896584-8818260"/>
     <hyperlink ref="B43" location="'📥进货表'!A13" display="3316801045105008960"/>
-    <hyperlink ref="C43" location="'📤销售表'!A41" display="249-0736245-4273400"/>
-    <hyperlink ref="B44" location="'📥进货表'!A14" display="3316818973003008960"/>
-    <hyperlink ref="C44" location="'📤销售表'!A38" display="503-1271944-7392630"/>
-    <hyperlink ref="B45" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C45" location="'📤销售表'!A42" display="503-8823986-1859812"/>
+    <hyperlink ref="C43" location="'📤销售表'!A40" display="249-3155796-5912651"/>
+    <hyperlink ref="B44" location="'📥进货表'!A13" display="3316801045105008960"/>
+    <hyperlink ref="C44" location="'📤销售表'!A41" display="249-0736245-4273400"/>
+    <hyperlink ref="B45" location="'📥进货表'!A14" display="3316818973003008960"/>
+    <hyperlink ref="C45" location="'📤销售表'!A38" display="503-1271944-7392630"/>
     <hyperlink ref="B46" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C46" location="'📤销售表'!A43" display="503-9622492-9545465"/>
+    <hyperlink ref="C46" location="'📤销售表'!A42" display="503-8823986-1859812"/>
     <hyperlink ref="B47" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C47" location="'📤销售表'!A44" display="249-4753098-4602218"/>
+    <hyperlink ref="C47" location="'📤销售表'!A43" display="503-9622492-9545465"/>
     <hyperlink ref="B48" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C48" location="'📤销售表'!A47" display="249-6190540-1277415"/>
+    <hyperlink ref="C48" location="'📤销售表'!A44" display="249-4753098-4602218"/>
     <hyperlink ref="B49" location="'📥进货表'!A15" display="3316818145041008960"/>
-    <hyperlink ref="C49" location="'📤销售表'!A48" display="250-4684901-9947011"/>
+    <hyperlink ref="C49" location="'📤销售表'!A47" display="249-6190540-1277415"/>
+    <hyperlink ref="B50" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C50" location="'📤销售表'!A48" display="250-4684901-9947011"/>
+    <hyperlink ref="B51" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C51" location="'📤销售表'!A51" display="249-7820833-4454235"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4217,25 +4217,76 @@
       </c>
       <c r="N51" s="27" t="n"/>
     </row>
-    <row r="52"/>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D52" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H52" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J52" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K52" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L52" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M52" s="25" t="inlineStr">
+        <is>
+          <t>249-3540468-0515047</t>
+        </is>
+      </c>
+      <c r="N52" s="27" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I53" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 60,748</t>
-        </is>
-      </c>
-      <c r="M53" s="32" t="inlineStr">
-        <is>
-          <t>49 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
+      <c r="I54" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 62,421</t>
+        </is>
+      </c>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>50 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="55"/>
     <row r="56"/>
     <row r="57"/>
@@ -4386,9 +4437,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="I54:L54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4510,7 +4561,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>7.12</v>
@@ -4519,11 +4570,11 @@
         <v>46262.34563657407</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (4个)</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4714,7 @@
         </is>
       </c>
       <c r="D10" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
@@ -6921,49 +6972,82 @@
       </c>
       <c r="B51" s="36" t="inlineStr">
         <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>249-3540468-0515047</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F51" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H51" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="36" t="inlineStr">
+        <is>
           <t>3316385967122008960</t>
         </is>
       </c>
-      <c r="C51" s="36" t="inlineStr">
+      <c r="C52" s="36" t="inlineStr">
         <is>
           <t>249-7820833-4454235</t>
         </is>
       </c>
-      <c r="D51" s="27" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
-      <c r="E51" s="27" t="inlineStr">
+      <c r="E52" s="27" t="inlineStr">
         <is>
           <t>绿色</t>
         </is>
       </c>
-      <c r="F51" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="29" t="n">
+      <c r="F52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="29" t="n">
         <v>4.58</v>
       </c>
-      <c r="H51" s="34" t="n">
+      <c r="H52" s="34" t="n">
         <v>929</v>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="53"/>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G53" s="31" t="n">
-        <v>294.89</v>
-      </c>
-      <c r="H53" s="35" t="n">
-        <v>60748</v>
-      </c>
-    </row>
-    <row r="54"/>
+      <c r="G54" s="31" t="n">
+        <v>302.43</v>
+      </c>
+      <c r="H54" s="35" t="n">
+        <v>62421</v>
+      </c>
+    </row>
     <row r="55"/>
     <row r="56"/>
     <row r="57"/>
@@ -7114,7 +7198,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A54:E54"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -7214,8 +7298,10 @@
     <hyperlink ref="C49" location="'📤销售表'!A47" display="249-6190540-1277415"/>
     <hyperlink ref="B50" location="'📥进货表'!A15" display="3316818145041008960"/>
     <hyperlink ref="C50" location="'📤销售表'!A48" display="250-4684901-9947011"/>
-    <hyperlink ref="B51" location="'📥进货表'!A16" display="3316385967122008960"/>
-    <hyperlink ref="C51" location="'📤销售表'!A51" display="249-7820833-4454235"/>
+    <hyperlink ref="B51" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C51" location="'📤销售表'!A52" display="249-3540468-0515047"/>
+    <hyperlink ref="B52" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C52" location="'📤销售表'!A51" display="249-7820833-4454235"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1355,23 +1355,64 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="27" t="inlineStr">
+        <is>
+          <t>33168296295145353</t>
+        </is>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="27" t="inlineStr">
+        <is>
+          <t>新商品牙膏首单</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G18" s="31" t="n">
-        <v>367.67</v>
-      </c>
-      <c r="H18" s="32" t="inlineStr">
-        <is>
-          <t>14 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="G19" s="31" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>15 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
@@ -1558,8 +1599,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4269,25 +4310,76 @@
       </c>
       <c r="N52" s="27" t="n"/>
     </row>
-    <row r="53"/>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C53" s="33" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D53" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
+        </is>
+      </c>
+      <c r="F53" s="27" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="inlineStr">
+        <is>
+          <t>PC-WS7Y-JVPR</t>
+        </is>
+      </c>
+      <c r="H53" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="34" t="n">
+        <v>1480</v>
+      </c>
+      <c r="J53" s="34" t="n">
+        <v>135</v>
+      </c>
+      <c r="K53" s="34" t="n">
+        <v>124</v>
+      </c>
+      <c r="L53" s="34" t="n">
+        <v>1356</v>
+      </c>
+      <c r="M53" s="25" t="inlineStr">
+        <is>
+          <t>250-3137793-8739864</t>
+        </is>
+      </c>
+      <c r="N53" s="27" t="n"/>
+    </row>
+    <row r="54"/>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I54" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 62,421</t>
-        </is>
-      </c>
-      <c r="M54" s="32" t="inlineStr">
-        <is>
-          <t>50 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
+      <c r="I55" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 63,777</t>
+        </is>
+      </c>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>51 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
@@ -4437,9 +4529,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I54:L54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="I55:L55"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4706,23 +4798,54 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>46274</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H9" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D11" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>6 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>7 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
@@ -4916,8 +5039,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7034,21 +7157,54 @@
         <v>929</v>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="25" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="36" t="inlineStr">
+        <is>
+          <t>33168296295145353</t>
+        </is>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>250-3137793-8739864</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="34" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G54" s="31" t="n">
-        <v>302.43</v>
-      </c>
-      <c r="H54" s="35" t="n">
-        <v>62421</v>
-      </c>
-    </row>
-    <row r="55"/>
+      <c r="G55" s="31" t="n">
+        <v>305.43</v>
+      </c>
+      <c r="H55" s="35" t="n">
+        <v>63777</v>
+      </c>
+    </row>
     <row r="56"/>
     <row r="57"/>
     <row r="58"/>
@@ -7198,7 +7354,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -7302,6 +7458,8 @@
     <hyperlink ref="C51" location="'📤销售表'!A52" display="249-3540468-0515047"/>
     <hyperlink ref="B52" location="'📥进货表'!A16" display="3316385967122008960"/>
     <hyperlink ref="C52" location="'📤销售表'!A51" display="249-7820833-4454235"/>
+    <hyperlink ref="B53" location="'📥进货表'!A17" display="33168296295145353"/>
+    <hyperlink ref="C53" location="'📤销售表'!A53" display="250-3137793-8739864"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4362,26 +4362,128 @@
       </c>
       <c r="N53" s="27" t="n"/>
     </row>
-    <row r="54"/>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="30" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="25" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C54" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D54" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F54" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H54" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J54" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K54" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L54" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M54" s="25" t="inlineStr">
+        <is>
+          <t>503-0712587-8403851</t>
+        </is>
+      </c>
+      <c r="N54" s="27" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="25" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C55" s="33" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D55" s="33" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F55" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G55" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H55" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J55" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K55" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L55" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M55" s="25" t="inlineStr">
+        <is>
+          <t>249-7475939-6250209</t>
+        </is>
+      </c>
+      <c r="N55" s="27" t="n"/>
+    </row>
+    <row r="56"/>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I55" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 63,777</t>
-        </is>
-      </c>
-      <c r="M55" s="32" t="inlineStr">
-        <is>
-          <t>51 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
+      <c r="I57" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 67,123</t>
+        </is>
+      </c>
+      <c r="M57" s="32" t="inlineStr">
+        <is>
+          <t>53 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="58"/>
     <row r="59"/>
     <row r="60"/>
@@ -4529,9 +4631,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="I55:L55"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="I57:L57"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4653,7 +4755,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>7.12</v>
@@ -4662,11 +4764,11 @@
         <v>46262.34563657407</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>库存充足 (1个)</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4940,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -7129,32 +7231,32 @@
       </c>
       <c r="B52" s="36" t="inlineStr">
         <is>
-          <t>3316385967122008960</t>
+          <t>3316818145041008960</t>
         </is>
       </c>
       <c r="C52" s="36" t="inlineStr">
         <is>
-          <t>249-7820833-4454235</t>
+          <t>503-0712587-8403851</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>切蒜器带透明收纳容器</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F52" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>4.58</v>
+        <v>7.54</v>
       </c>
       <c r="H52" s="34" t="n">
-        <v>929</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1">
@@ -7163,50 +7265,116 @@
       </c>
       <c r="B53" s="36" t="inlineStr">
         <is>
+          <t>3316818145041008960</t>
+        </is>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>249-7475939-6250209</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F53" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="29" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="H53" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="25" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="36" t="inlineStr">
+        <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="C54" s="36" t="inlineStr">
+        <is>
+          <t>249-7820833-4454235</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E54" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F54" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H54" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="25" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="36" t="inlineStr">
+        <is>
           <t>33168296295145353</t>
         </is>
       </c>
-      <c r="C53" s="36" t="inlineStr">
+      <c r="C55" s="36" t="inlineStr">
         <is>
           <t>250-3137793-8739864</t>
         </is>
       </c>
-      <c r="D53" s="27" t="inlineStr">
+      <c r="D55" s="27" t="inlineStr">
         <is>
           <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
-      <c r="E53" s="27" t="inlineStr">
+      <c r="E55" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="F53" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="29" t="n">
+      <c r="F55" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="34" t="n">
+      <c r="H55" s="34" t="n">
         <v>1356</v>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="30" t="inlineStr">
+    <row r="56"/>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G55" s="31" t="n">
-        <v>305.43</v>
-      </c>
-      <c r="H55" s="35" t="n">
-        <v>63777</v>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
+      <c r="G57" s="31" t="n">
+        <v>320.51</v>
+      </c>
+      <c r="H57" s="35" t="n">
+        <v>67123</v>
+      </c>
+    </row>
     <row r="58"/>
     <row r="59"/>
     <row r="60"/>
@@ -7354,7 +7522,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -7456,10 +7624,14 @@
     <hyperlink ref="C50" location="'📤销售表'!A48" display="250-4684901-9947011"/>
     <hyperlink ref="B51" location="'📥进货表'!A15" display="3316818145041008960"/>
     <hyperlink ref="C51" location="'📤销售表'!A52" display="249-3540468-0515047"/>
-    <hyperlink ref="B52" location="'📥进货表'!A16" display="3316385967122008960"/>
-    <hyperlink ref="C52" location="'📤销售表'!A51" display="249-7820833-4454235"/>
-    <hyperlink ref="B53" location="'📥进货表'!A17" display="33168296295145353"/>
-    <hyperlink ref="C53" location="'📤销售表'!A53" display="250-3137793-8739864"/>
+    <hyperlink ref="B52" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C52" location="'📤销售表'!A54" display="503-0712587-8403851"/>
+    <hyperlink ref="B53" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C53" location="'📤销售表'!A55" display="249-7475939-6250209"/>
+    <hyperlink ref="B54" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C54" location="'📤销售表'!A51" display="249-7820833-4454235"/>
+    <hyperlink ref="B55" location="'📥进货表'!A17" display="33168296295145353"/>
+    <hyperlink ref="C55" location="'📤销售表'!A53" display="250-3137793-8739864"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4466,26 +4466,128 @@
       </c>
       <c r="N55" s="27" t="n"/>
     </row>
-    <row r="56"/>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="30" t="inlineStr">
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="25" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C56" s="33" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D56" s="33" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F56" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H56" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J56" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K56" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L56" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M56" s="25" t="inlineStr">
+        <is>
+          <t>503-4315727-6147862</t>
+        </is>
+      </c>
+      <c r="N56" s="27" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C57" s="33" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D57" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F57" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G57" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H57" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J57" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K57" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L57" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M57" s="25" t="inlineStr">
+        <is>
+          <t>249-1288946-1675069</t>
+        </is>
+      </c>
+      <c r="N57" s="27" t="n"/>
+    </row>
+    <row r="58"/>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I57" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 67,123</t>
-        </is>
-      </c>
-      <c r="M57" s="32" t="inlineStr">
-        <is>
-          <t>53 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 69,725</t>
+        </is>
+      </c>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>55 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="60"/>
     <row r="61"/>
     <row r="62"/>
@@ -4631,9 +4733,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="I57:L57"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="I59:L59"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4723,7 +4825,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.61</v>
@@ -4732,11 +4834,11 @@
         <v>46270</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46270</v>
+        <v>46281</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (8个)</t>
+          <t>库存充足 (7个)</t>
         </is>
       </c>
     </row>
@@ -4746,29 +4848,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>7.12</v>
+        <v>5.9</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46262.34563657407</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46275</v>
+        <v>46214</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (1个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -4778,25 +4880,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -4810,25 +4912,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>6.08</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46268</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -4842,25 +4944,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>6.08</v>
+        <v>7.12</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46262.34563657407</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46268</v>
+        <v>46280</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -4940,7 +5042,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -7299,32 +7401,32 @@
       </c>
       <c r="B54" s="36" t="inlineStr">
         <is>
-          <t>3316385967122008960</t>
+          <t>3316818145041008960</t>
         </is>
       </c>
       <c r="C54" s="36" t="inlineStr">
         <is>
-          <t>249-7820833-4454235</t>
+          <t>249-1288946-1675069</t>
         </is>
       </c>
       <c r="D54" s="27" t="inlineStr">
         <is>
-          <t>切蒜器带透明收纳容器</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F54" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>4.58</v>
+        <v>7.54</v>
       </c>
       <c r="H54" s="34" t="n">
-        <v>929</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1">
@@ -7333,50 +7435,116 @@
       </c>
       <c r="B55" s="36" t="inlineStr">
         <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>249-7820833-4454235</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F55" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H55" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="25" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="36" t="inlineStr">
+        <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="C56" s="36" t="inlineStr">
+        <is>
+          <t>503-4315727-6147862</t>
+        </is>
+      </c>
+      <c r="D56" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E56" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F56" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H56" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="36" t="inlineStr">
+        <is>
           <t>33168296295145353</t>
         </is>
       </c>
-      <c r="C55" s="36" t="inlineStr">
+      <c r="C57" s="36" t="inlineStr">
         <is>
           <t>250-3137793-8739864</t>
         </is>
       </c>
-      <c r="D55" s="27" t="inlineStr">
+      <c r="D57" s="27" t="inlineStr">
         <is>
           <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
-      <c r="E55" s="27" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="F55" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="29" t="n">
+      <c r="F57" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="34" t="n">
+      <c r="H57" s="34" t="n">
         <v>1356</v>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="30" t="inlineStr">
+    <row r="58"/>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G57" s="31" t="n">
-        <v>320.51</v>
-      </c>
-      <c r="H57" s="35" t="n">
-        <v>67123</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
+      <c r="G59" s="31" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="H59" s="35" t="n">
+        <v>69725</v>
+      </c>
+    </row>
     <row r="60"/>
     <row r="61"/>
     <row r="62"/>
@@ -7522,7 +7690,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -7628,10 +7796,14 @@
     <hyperlink ref="C52" location="'📤销售表'!A54" display="503-0712587-8403851"/>
     <hyperlink ref="B53" location="'📥进货表'!A15" display="3316818145041008960"/>
     <hyperlink ref="C53" location="'📤销售表'!A55" display="249-7475939-6250209"/>
-    <hyperlink ref="B54" location="'📥进货表'!A16" display="3316385967122008960"/>
-    <hyperlink ref="C54" location="'📤销售表'!A51" display="249-7820833-4454235"/>
-    <hyperlink ref="B55" location="'📥进货表'!A17" display="33168296295145353"/>
-    <hyperlink ref="C55" location="'📤销售表'!A53" display="250-3137793-8739864"/>
+    <hyperlink ref="B54" location="'📥进货表'!A15" display="3316818145041008960"/>
+    <hyperlink ref="C54" location="'📤销售表'!A57" display="249-1288946-1675069"/>
+    <hyperlink ref="B55" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C55" location="'📤销售表'!A51" display="249-7820833-4454235"/>
+    <hyperlink ref="B56" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C56" location="'📤销售表'!A56" display="503-4315727-6147862"/>
+    <hyperlink ref="B57" location="'📥进货表'!A17" display="33168296295145353"/>
+    <hyperlink ref="C57" location="'📤销售表'!A53" display="250-3137793-8739864"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -12,6 +12,7 @@
     <sheet name="📦库存表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="❌库存遗失表" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="🔗关联视图" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="📦出货记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,12 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -238,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -344,6 +344,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -709,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1397,7 +1399,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
@@ -1412,190 +1413,9 @@
           <t>15 笔进货</t>
         </is>
       </c>
-    </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
+      <c r="I19" s="37" t="n"/>
+      <c r="J19" s="38" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
@@ -1612,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4570,7 +4390,6 @@
       </c>
       <c r="N57" s="27" t="n"/>
     </row>
-    <row r="58"/>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="30" t="inlineStr">
         <is>
@@ -4582,155 +4401,16 @@
           <t>总销售额: JPY 69,725</t>
         </is>
       </c>
+      <c r="J59" s="37" t="n"/>
+      <c r="K59" s="37" t="n"/>
+      <c r="L59" s="38" t="n"/>
       <c r="M59" s="32" t="inlineStr">
         <is>
           <t>55 笔销售</t>
         </is>
       </c>
-    </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
+      <c r="N59" s="38" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="M59:N59"/>
@@ -4748,7 +4428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5034,7 +4714,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
@@ -5049,198 +4728,10 @@
           <t>7 种商品</t>
         </is>
       </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
+      <c r="F11" s="37" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="38" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:H11"/>
@@ -5257,7 +4748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5364,7 +4855,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="30" t="inlineStr">
         <is>
@@ -5382,204 +4872,10 @@
           <t>1 笔遗失记录</t>
         </is>
       </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
+      <c r="G5" s="37" t="n"/>
+      <c r="H5" s="37" t="n"/>
+      <c r="I5" s="38" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -5599,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7531,7 +6827,6 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="58"/>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="30" t="inlineStr">
         <is>
@@ -7545,149 +6840,6 @@
         <v>69725</v>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A59:E59"/>
@@ -7807,4 +6959,100 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>📦 出货记录表 (2026年)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>出货平台</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>订购日期</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>发货日期</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>商品名称</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>规格</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>销售价(日元)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>税金(日元)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>手续费(日元)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>销售额(日元)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>出货订单号</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>关联购买记录</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -12,7 +12,6 @@
     <sheet name="📦库存表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="❌库存遗失表" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="🔗关联视图" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="📦出货记录" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="¥#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="&quot;JPY&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1399,6 +1399,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="30" t="inlineStr">
         <is>
@@ -1413,9 +1414,190 @@
           <t>15 笔进货</t>
         </is>
       </c>
-      <c r="I19" s="37" t="n"/>
-      <c r="J19" s="38" t="n"/>
-    </row>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
@@ -1432,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4390,32 +4572,325 @@
       </c>
       <c r="N57" s="27" t="n"/>
     </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D58" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H58" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J58" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K58" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L58" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M58" s="25" t="inlineStr">
+        <is>
+          <t>250-5859552-6451816</t>
+        </is>
+      </c>
+      <c r="N58" s="27" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="n">
+        <v>46284</v>
+      </c>
+      <c r="D59" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G59" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H59" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J59" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K59" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L59" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M59" s="25" t="inlineStr">
+        <is>
+          <t>503-9561108-9461422</t>
+        </is>
+      </c>
+      <c r="N59" s="27" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C60" s="33" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D60" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G60" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H60" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J60" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K60" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L60" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M60" s="25" t="inlineStr">
+        <is>
+          <t>503-2286952-6588608</t>
+        </is>
+      </c>
+      <c r="N60" s="27" t="n"/>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I59" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 69,725</t>
-        </is>
-      </c>
-      <c r="J59" s="37" t="n"/>
-      <c r="K59" s="37" t="n"/>
-      <c r="L59" s="38" t="n"/>
-      <c r="M59" s="32" t="inlineStr">
-        <is>
-          <t>55 笔销售</t>
-        </is>
-      </c>
-      <c r="N59" s="38" t="n"/>
-    </row>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 74,000</t>
+        </is>
+      </c>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>58 笔销售</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="I59:L59"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="I62:L62"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4428,7 +4903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4505,7 +4980,7 @@
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="29" t="n">
         <v>4.61</v>
@@ -4514,11 +4989,11 @@
         <v>46270</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46281</v>
+        <v>46284</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (7个)</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -4714,6 +5189,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="30" t="inlineStr">
         <is>
@@ -4721,17 +5197,205 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
           <t>7 种商品</t>
         </is>
       </c>
-      <c r="F11" s="37" t="n"/>
-      <c r="G11" s="37" t="n"/>
-      <c r="H11" s="38" t="n"/>
-    </row>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:H11"/>
@@ -4748,7 +5412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4855,6 +5519,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="30" t="inlineStr">
         <is>
@@ -4872,10 +5537,204 @@
           <t>1 笔遗失记录</t>
         </is>
       </c>
-      <c r="G5" s="37" t="n"/>
-      <c r="H5" s="37" t="n"/>
-      <c r="I5" s="38" t="n"/>
-    </row>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
@@ -4895,7 +5754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6799,50 +7658,293 @@
       </c>
       <c r="B57" s="36" t="inlineStr">
         <is>
+          <t>3316385967122008960</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>503-9561108-9461422</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="F57" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="29" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H57" s="34" t="n">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="36" t="inlineStr">
+        <is>
           <t>33168296295145353</t>
         </is>
       </c>
-      <c r="C57" s="36" t="inlineStr">
+      <c r="C58" s="36" t="inlineStr">
         <is>
           <t>250-3137793-8739864</t>
         </is>
       </c>
-      <c r="D57" s="27" t="inlineStr">
+      <c r="D58" s="27" t="inlineStr">
         <is>
           <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="F57" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="29" t="n">
+      <c r="F58" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="34" t="n">
+      <c r="H58" s="34" t="n">
         <v>1356</v>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="25" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>250-5859552-6451816</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F59" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C60" s="36" t="inlineStr">
+        <is>
+          <t>503-2286952-6588608</t>
+        </is>
+      </c>
+      <c r="D60" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F60" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G59" s="31" t="n">
-        <v>332.63</v>
-      </c>
-      <c r="H59" s="35" t="n">
-        <v>69725</v>
-      </c>
-    </row>
+      <c r="G62" s="31" t="n">
+        <v>337.21</v>
+      </c>
+      <c r="H62" s="35" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A62:E62"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -6954,105 +8056,13 @@
     <hyperlink ref="C55" location="'📤销售表'!A51" display="249-7820833-4454235"/>
     <hyperlink ref="B56" location="'📥进货表'!A16" display="3316385967122008960"/>
     <hyperlink ref="C56" location="'📤销售表'!A56" display="503-4315727-6147862"/>
-    <hyperlink ref="B57" location="'📥进货表'!A17" display="33168296295145353"/>
-    <hyperlink ref="C57" location="'📤销售表'!A53" display="250-3137793-8739864"/>
+    <hyperlink ref="B57" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C57" location="'📤销售表'!A59" display="503-9561108-9461422"/>
+    <hyperlink ref="B58" location="'📥进货表'!A17" display="33168296295145353"/>
+    <hyperlink ref="C58" location="'📤销售表'!A53" display="250-3137793-8739864"/>
+    <hyperlink ref="C59" location="'📤销售表'!A58" display="250-5859552-6451816"/>
+    <hyperlink ref="C60" location="'📤销售表'!A60" display="503-2286952-6588608"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>📦 出货记录表 (2026年)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>出货平台</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>订购日期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>发货日期</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>商品名称</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>规格</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>SKU</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>销售价(日元)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>税金(日元)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>手续费(日元)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>销售额(日元)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>出货订单号</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>关联购买记录</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1399,23 +1399,64 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>46284.68633101852</v>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX塑料除黄剂</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>100ml+毛巾</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J18" s="27" t="inlineStr">
+        <is>
+          <t>补货10个（商品65+运费9.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G19" s="31" t="n">
-        <v>370.67</v>
-      </c>
-      <c r="H19" s="32" t="inlineStr">
-        <is>
-          <t>15 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="G20" s="31" t="n">
+        <v>445.17</v>
+      </c>
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>16 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
@@ -1601,8 +1642,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="H20:J20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4971,29 +5012,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.61</v>
+        <v>7.24</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46270</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -5003,29 +5044,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>5.9</v>
+        <v>4.61</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46270</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46214</v>
+        <v>46284</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -5035,25 +5076,25 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
@@ -5067,25 +5108,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>6.08</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46268</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -5099,25 +5140,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>7.12</v>
+        <v>6.08</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46262.34563657407</v>
+        <v>46251.90046296296</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46280</v>
+        <v>46268</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -5197,7 +5238,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -7724,9 +7765,9 @@
       <c r="A59" s="25" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C59" s="36" t="inlineStr">
@@ -7748,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="G59" s="29" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="H59" s="34" t="n">
         <v>1673</v>
@@ -7758,9 +7799,9 @@
       <c r="A60" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B60" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C60" s="36" t="inlineStr">
@@ -7782,7 +7823,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="29" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="H60" s="34" t="n">
         <v>1673</v>
@@ -7796,7 +7837,7 @@
         </is>
       </c>
       <c r="G62" s="31" t="n">
-        <v>337.21</v>
+        <v>352.11</v>
       </c>
       <c r="H62" s="35" t="n">
         <v>74000</v>
@@ -8060,7 +8101,9 @@
     <hyperlink ref="C57" location="'📤销售表'!A59" display="503-9561108-9461422"/>
     <hyperlink ref="B58" location="'📥进货表'!A17" display="33168296295145353"/>
     <hyperlink ref="C58" location="'📤销售表'!A53" display="250-3137793-8739864"/>
+    <hyperlink ref="B59" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C59" location="'📤销售表'!A58" display="250-5859552-6451816"/>
+    <hyperlink ref="B60" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C60" location="'📤销售表'!A60" display="503-2286952-6588608"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4769,26 +4769,128 @@
       </c>
       <c r="N60" s="27" t="n"/>
     </row>
-    <row r="61"/>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C61" s="33" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D61" s="33" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H61" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J61" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K61" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L61" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M61" s="25" t="inlineStr">
+        <is>
+          <t>249-1402244-3486251</t>
+        </is>
+      </c>
+      <c r="N61" s="27" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C62" s="33" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D62" s="33" t="n">
+        <v>46288</v>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G62" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H62" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J62" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K62" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L62" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M62" s="25" t="inlineStr">
+        <is>
+          <t>249-2888479-8452654</t>
+        </is>
+      </c>
+      <c r="N62" s="27" t="n"/>
+    </row>
+    <row r="63"/>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I62" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 74,000</t>
-        </is>
-      </c>
-      <c r="M62" s="32" t="inlineStr">
-        <is>
-          <t>58 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64"/>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 77,346</t>
+        </is>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>60 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="65"/>
     <row r="66"/>
     <row r="67"/>
@@ -4929,9 +5031,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M62:N62"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="I64:L64"/>
+    <mergeCell ref="M64:N64"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5012,29 +5114,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>7.24</v>
+        <v>4.61</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46270</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (8个)</t>
+          <t>库存充足 (6个)</t>
         </is>
       </c>
     </row>
@@ -5044,25 +5146,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>6</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>4.61</v>
+        <v>7.24</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46270</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -5238,7 +5340,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -7806,7 +7908,7 @@
       </c>
       <c r="C60" s="36" t="inlineStr">
         <is>
-          <t>503-2286952-6588608</t>
+          <t>249-1402244-3486251</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -7829,22 +7931,88 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="30" t="inlineStr">
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C61" s="36" t="inlineStr">
+        <is>
+          <t>503-2286952-6588608</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F61" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H61" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C62" s="36" t="inlineStr">
+        <is>
+          <t>249-2888479-8452654</t>
+        </is>
+      </c>
+      <c r="D62" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F62" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H62" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G62" s="31" t="n">
-        <v>352.11</v>
-      </c>
-      <c r="H62" s="35" t="n">
-        <v>74000</v>
-      </c>
-    </row>
-    <row r="63"/>
-    <row r="64"/>
+      <c r="G64" s="31" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="H64" s="35" t="n">
+        <v>77346</v>
+      </c>
+    </row>
     <row r="65"/>
     <row r="66"/>
     <row r="67"/>
@@ -7985,7 +8153,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A62:E62"/>
+    <mergeCell ref="A64:E64"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8104,7 +8272,11 @@
     <hyperlink ref="B59" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C59" location="'📤销售表'!A58" display="250-5859552-6451816"/>
     <hyperlink ref="B60" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C60" location="'📤销售表'!A60" display="503-2286952-6588608"/>
+    <hyperlink ref="C60" location="'📤销售表'!A61" display="249-1402244-3486251"/>
+    <hyperlink ref="B61" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C61" location="'📤销售表'!A60" display="503-2286952-6588608"/>
+    <hyperlink ref="B62" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4873,25 +4873,76 @@
       </c>
       <c r="N62" s="27" t="n"/>
     </row>
-    <row r="63"/>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C63" s="33" t="n">
+        <v>46288</v>
+      </c>
+      <c r="D63" s="33" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H63" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J63" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K63" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L63" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M63" s="25" t="inlineStr">
+        <is>
+          <t>249-3209029-9999810</t>
+        </is>
+      </c>
+      <c r="N63" s="27" t="n"/>
+    </row>
+    <row r="64"/>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 77,346</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>60 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 79,019</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>61 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>
@@ -5031,9 +5082,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="I64:L64"/>
-    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="I65:L65"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5155,7 +5206,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>7.24</v>
@@ -5164,11 +5215,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5391,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -7999,21 +8050,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="30" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="25" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C63" s="36" t="inlineStr">
+        <is>
+          <t>249-3209029-9999810</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F63" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H63" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G64" s="31" t="n">
-        <v>367.01</v>
-      </c>
-      <c r="H64" s="35" t="n">
-        <v>77346</v>
-      </c>
-    </row>
-    <row r="65"/>
+      <c r="G65" s="31" t="n">
+        <v>374.46</v>
+      </c>
+      <c r="H65" s="35" t="n">
+        <v>79019</v>
+      </c>
+    </row>
     <row r="66"/>
     <row r="67"/>
     <row r="68"/>
@@ -8153,7 +8237,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8277,6 +8361,8 @@
     <hyperlink ref="C61" location="'📤销售表'!A60" display="503-2286952-6588608"/>
     <hyperlink ref="B62" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
+    <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4925,25 +4925,76 @@
       </c>
       <c r="N63" s="27" t="n"/>
     </row>
-    <row r="64"/>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C64" s="33" t="n">
+        <v>46291</v>
+      </c>
+      <c r="D64" s="33" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G64" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H64" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J64" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K64" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L64" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M64" s="25" t="inlineStr">
+        <is>
+          <t>249-9986134-0069209</t>
+        </is>
+      </c>
+      <c r="N64" s="27" t="n"/>
+    </row>
+    <row r="65"/>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I65" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 79,019</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>61 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 80,692</t>
+        </is>
+      </c>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>62 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="67"/>
     <row r="68"/>
     <row r="69"/>
@@ -5082,9 +5133,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="I65:L65"/>
+    <mergeCell ref="I66:L66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5206,7 +5257,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>7.24</v>
@@ -5215,11 +5266,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46288</v>
+        <v>46291</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (4个)</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5442,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8084,21 +8135,54 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="64"/>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="36" t="inlineStr">
+        <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>249-9986134-0069209</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F64" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H64" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G65" s="31" t="n">
-        <v>374.46</v>
-      </c>
-      <c r="H65" s="35" t="n">
-        <v>79019</v>
-      </c>
-    </row>
-    <row r="66"/>
+      <c r="G66" s="31" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="H66" s="35" t="n">
+        <v>80692</v>
+      </c>
+    </row>
     <row r="67"/>
     <row r="68"/>
     <row r="69"/>
@@ -8237,7 +8321,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8363,6 +8447,8 @@
     <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
     <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
+    <hyperlink ref="B64" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C64" location="'📤销售表'!A64" display="249-9986134-0069209"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -4935,44 +4935,44 @@
         </is>
       </c>
       <c r="C64" s="33" t="n">
-        <v>46291</v>
+        <v>46289</v>
       </c>
       <c r="D64" s="33" t="n">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="F64" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="G64" s="25" t="inlineStr">
         <is>
-          <t>asd159</t>
+          <t>1X-GB0W-BY30</t>
         </is>
       </c>
       <c r="H64" s="28" t="n">
         <v>1</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>1468</v>
+        <v>1122</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="K64" s="34" t="n">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="L64" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
       <c r="M64" s="25" t="inlineStr">
         <is>
-          <t>249-9986134-0069209</t>
+          <t>249-0470172-4818202</t>
         </is>
       </c>
       <c r="N64" s="27" t="n"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="I66" s="32" t="inlineStr">
         <is>
-          <t>总销售额: JPY 80,692</t>
+          <t>总销售额: JPY 80,024</t>
         </is>
       </c>
       <c r="M66" s="32" t="inlineStr">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="29" t="n">
         <v>7.24</v>
@@ -5266,11 +5266,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (4个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8139,34 +8139,34 @@
       <c r="A64" s="25" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="36" t="inlineStr">
-        <is>
-          <t>3316423695109035788</t>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
         </is>
       </c>
       <c r="C64" s="36" t="inlineStr">
         <is>
-          <t>249-9986134-0069209</t>
+          <t>249-0470172-4818202</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F64" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="29" t="n">
-        <v>7.45</v>
+        <v>0</v>
       </c>
       <c r="H64" s="34" t="n">
-        <v>1673</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="65"/>
@@ -8177,10 +8177,10 @@
         </is>
       </c>
       <c r="G66" s="31" t="n">
-        <v>381.91</v>
+        <v>374.46</v>
       </c>
       <c r="H66" s="35" t="n">
-        <v>80692</v>
+        <v>80024</v>
       </c>
     </row>
     <row r="67"/>
@@ -8447,8 +8447,7 @@
     <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
     <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
-    <hyperlink ref="B64" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C64" location="'📤销售表'!A64" display="249-9986134-0069209"/>
+    <hyperlink ref="C64" location="'📤销售表'!A64" display="249-0470172-4818202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1441,23 +1441,64 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX玻璃修复膏</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>50g+海绵</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="29" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>3316454223181008960</t>
+        </is>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>补货6套（商品33+运费6.5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G20" s="31" t="n">
-        <v>445.17</v>
-      </c>
-      <c r="H20" s="32" t="inlineStr">
-        <is>
-          <t>16 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="G21" s="31" t="n">
+        <v>484.67</v>
+      </c>
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>17 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -1641,9 +1682,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5248,25 +5289,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>7.24</v>
+        <v>6.33</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46293</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -5280,29 +5321,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>7.24</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46288</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -5312,25 +5353,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -5344,25 +5385,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>6.08</v>
+        <v>20</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46251.90046296296</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46268</v>
+        <v>46221</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -5442,7 +5483,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8139,9 +8180,9 @@
       <c r="A64" s="25" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B64" s="36" t="inlineStr">
+        <is>
+          <t>3316454223181008960</t>
         </is>
       </c>
       <c r="C64" s="36" t="inlineStr">
@@ -8163,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="29" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="H64" s="34" t="n">
         <v>1005</v>
@@ -8177,7 +8218,7 @@
         </is>
       </c>
       <c r="G66" s="31" t="n">
-        <v>374.46</v>
+        <v>381.04</v>
       </c>
       <c r="H66" s="35" t="n">
         <v>80024</v>
@@ -8447,6 +8488,7 @@
     <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
     <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
+    <hyperlink ref="B64" location="'📥进货表'!A19" display="3316454223181008960"/>
     <hyperlink ref="C64" location="'📤销售表'!A64" display="249-0470172-4818202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -5018,25 +5018,76 @@
       </c>
       <c r="N64" s="27" t="n"/>
     </row>
-    <row r="65"/>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C65" s="33" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D65" s="33" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G65" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H65" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J65" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K65" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L65" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M65" s="25" t="inlineStr">
+        <is>
+          <t>503-8229948-4722203</t>
+        </is>
+      </c>
+      <c r="N65" s="27" t="n"/>
+    </row>
+    <row r="66"/>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 80,024</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>62 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 81,697</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>63 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="68"/>
     <row r="69"/>
     <row r="70"/>
@@ -5174,9 +5225,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I66:L66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="I67:L67"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5330,7 +5381,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>7.24</v>
@@ -5339,11 +5390,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (4个)</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5534,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8182,49 +8233,82 @@
       </c>
       <c r="B64" s="36" t="inlineStr">
         <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>503-8229948-4722203</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F64" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H64" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="36" t="inlineStr">
+        <is>
           <t>3316454223181008960</t>
         </is>
       </c>
-      <c r="C64" s="36" t="inlineStr">
+      <c r="C65" s="36" t="inlineStr">
         <is>
           <t>249-0470172-4818202</t>
         </is>
       </c>
-      <c r="D64" s="27" t="inlineStr">
+      <c r="D65" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="E65" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F64" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="29" t="n">
+      <c r="F65" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="29" t="n">
         <v>6.58</v>
       </c>
-      <c r="H64" s="34" t="n">
+      <c r="H65" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="65"/>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="66"/>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G66" s="31" t="n">
-        <v>381.04</v>
-      </c>
-      <c r="H66" s="35" t="n">
-        <v>80024</v>
-      </c>
-    </row>
-    <row r="67"/>
+      <c r="G67" s="31" t="n">
+        <v>388.49</v>
+      </c>
+      <c r="H67" s="35" t="n">
+        <v>81697</v>
+      </c>
+    </row>
     <row r="68"/>
     <row r="69"/>
     <row r="70"/>
@@ -8362,7 +8446,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A67:E67"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8488,8 +8572,10 @@
     <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
     <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
-    <hyperlink ref="B64" location="'📥进货表'!A19" display="3316454223181008960"/>
-    <hyperlink ref="C64" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="B64" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C64" location="'📤销售表'!A65" display="503-8229948-4722203"/>
+    <hyperlink ref="B65" location="'📥进货表'!A19" display="3316454223181008960"/>
+    <hyperlink ref="C65" location="'📤销售表'!A64" display="249-0470172-4818202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -5070,26 +5070,128 @@
       </c>
       <c r="N65" s="27" t="n"/>
     </row>
-    <row r="66"/>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C66" s="33" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D66" s="33" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>切蒜器带透明收纳容器</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="inlineStr">
+        <is>
+          <t>绿色</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="inlineStr">
+        <is>
+          <t>ba0010</t>
+        </is>
+      </c>
+      <c r="H66" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="34" t="n">
+        <v>699</v>
+      </c>
+      <c r="J66" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="K66" s="34" t="n">
+        <v>169</v>
+      </c>
+      <c r="L66" s="34" t="n">
+        <v>929</v>
+      </c>
+      <c r="M66" s="25" t="inlineStr">
+        <is>
+          <t>249-7468125-0482264</t>
+        </is>
+      </c>
+      <c r="N66" s="27" t="n"/>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C67" s="33" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D67" s="33" t="n">
+        <v>46297</v>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="F67" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="inlineStr">
+        <is>
+          <t>WD-FBTT-4QTJ</t>
+        </is>
+      </c>
+      <c r="H67" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="34" t="n">
+        <v>2888</v>
+      </c>
+      <c r="J67" s="34" t="n">
+        <v>263</v>
+      </c>
+      <c r="K67" s="34" t="n">
+        <v>445</v>
+      </c>
+      <c r="L67" s="34" t="n">
+        <v>2443</v>
+      </c>
+      <c r="M67" s="25" t="inlineStr">
+        <is>
+          <t>503-9041299-9070211</t>
+        </is>
+      </c>
+      <c r="N67" s="27" t="n"/>
+    </row>
+    <row r="68"/>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 81,697</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>63 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69"/>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 85,069</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>65 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="70"/>
     <row r="71"/>
     <row r="72"/>
@@ -5225,9 +5327,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="I67:L67"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="M69:N69"/>
+    <mergeCell ref="I69:L69"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5308,29 +5410,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>4.61</v>
+        <v>6.33</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46270</v>
+        <v>46293</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (6个)</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -5340,25 +5442,25 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
         <v>5</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>6.33</v>
+        <v>4.61</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46293</v>
+        <v>46270</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46289</v>
+        <v>46295</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
@@ -5534,7 +5636,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8029,32 +8131,32 @@
       </c>
       <c r="B58" s="36" t="inlineStr">
         <is>
-          <t>33168296295145353</t>
+          <t>3316385967122008960</t>
         </is>
       </c>
       <c r="C58" s="36" t="inlineStr">
         <is>
-          <t>250-3137793-8739864</t>
+          <t>249-7468125-0482264</t>
         </is>
       </c>
       <c r="D58" s="27" t="inlineStr">
         <is>
-          <t>韩伦美羽烟酰胺炫白牙膏</t>
+          <t>切蒜器带透明收纳容器</t>
         </is>
       </c>
       <c r="E58" s="27" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>绿色</t>
         </is>
       </c>
       <c r="F58" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="29" t="n">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="H58" s="34" t="n">
-        <v>1356</v>
+        <v>929</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
@@ -8063,32 +8165,32 @@
       </c>
       <c r="B59" s="36" t="inlineStr">
         <is>
-          <t>3316423695109035788</t>
+          <t>33168296295145353</t>
         </is>
       </c>
       <c r="C59" s="36" t="inlineStr">
         <is>
-          <t>250-5859552-6451816</t>
+          <t>250-3137793-8739864</t>
         </is>
       </c>
       <c r="D59" s="27" t="inlineStr">
         <is>
-          <t>塑料除黄剂 黄ばみ除去剤</t>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>100ml</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="F59" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="29" t="n">
-        <v>7.45</v>
+        <v>3</v>
       </c>
       <c r="H59" s="34" t="n">
-        <v>1673</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
@@ -8102,7 +8204,7 @@
       </c>
       <c r="C60" s="36" t="inlineStr">
         <is>
-          <t>249-1402244-3486251</t>
+          <t>250-5859552-6451816</t>
         </is>
       </c>
       <c r="D60" s="27" t="inlineStr">
@@ -8136,7 +8238,7 @@
       </c>
       <c r="C61" s="36" t="inlineStr">
         <is>
-          <t>503-2286952-6588608</t>
+          <t>249-1402244-3486251</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
@@ -8170,7 +8272,7 @@
       </c>
       <c r="C62" s="36" t="inlineStr">
         <is>
-          <t>249-2888479-8452654</t>
+          <t>503-2286952-6588608</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
@@ -8204,7 +8306,7 @@
       </c>
       <c r="C63" s="36" t="inlineStr">
         <is>
-          <t>249-3209029-9999810</t>
+          <t>249-2888479-8452654</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
@@ -8238,7 +8340,7 @@
       </c>
       <c r="C64" s="36" t="inlineStr">
         <is>
-          <t>503-8229948-4722203</t>
+          <t>249-3209029-9999810</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
@@ -8267,50 +8369,116 @@
       </c>
       <c r="B65" s="36" t="inlineStr">
         <is>
+          <t>3316423695109035788</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>503-8229948-4722203</t>
+        </is>
+      </c>
+      <c r="D65" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F65" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="H65" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="36" t="inlineStr">
+        <is>
           <t>3316454223181008960</t>
         </is>
       </c>
-      <c r="C65" s="36" t="inlineStr">
+      <c r="C66" s="36" t="inlineStr">
         <is>
           <t>249-0470172-4818202</t>
         </is>
       </c>
-      <c r="D65" s="27" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
-      <c r="E65" s="27" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="F65" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="29" t="n">
+      <c r="F66" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="29" t="n">
         <v>6.58</v>
       </c>
-      <c r="H65" s="34" t="n">
+      <c r="H66" s="34" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="66"/>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="25" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>503-9041299-9070211</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="F67" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="34" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G67" s="31" t="n">
-        <v>388.49</v>
-      </c>
-      <c r="H67" s="35" t="n">
-        <v>81697</v>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69"/>
+      <c r="G69" s="31" t="n">
+        <v>393.07</v>
+      </c>
+      <c r="H69" s="35" t="n">
+        <v>85069</v>
+      </c>
+    </row>
     <row r="70"/>
     <row r="71"/>
     <row r="72"/>
@@ -8446,7 +8614,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A69:E69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8560,22 +8728,25 @@
     <hyperlink ref="C56" location="'📤销售表'!A56" display="503-4315727-6147862"/>
     <hyperlink ref="B57" location="'📥进货表'!A16" display="3316385967122008960"/>
     <hyperlink ref="C57" location="'📤销售表'!A59" display="503-9561108-9461422"/>
-    <hyperlink ref="B58" location="'📥进货表'!A17" display="33168296295145353"/>
-    <hyperlink ref="C58" location="'📤销售表'!A53" display="250-3137793-8739864"/>
-    <hyperlink ref="B59" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C59" location="'📤销售表'!A58" display="250-5859552-6451816"/>
+    <hyperlink ref="B58" location="'📥进货表'!A16" display="3316385967122008960"/>
+    <hyperlink ref="C58" location="'📤销售表'!A66" display="249-7468125-0482264"/>
+    <hyperlink ref="B59" location="'📥进货表'!A17" display="33168296295145353"/>
+    <hyperlink ref="C59" location="'📤销售表'!A53" display="250-3137793-8739864"/>
     <hyperlink ref="B60" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C60" location="'📤销售表'!A61" display="249-1402244-3486251"/>
+    <hyperlink ref="C60" location="'📤销售表'!A58" display="250-5859552-6451816"/>
     <hyperlink ref="B61" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C61" location="'📤销售表'!A60" display="503-2286952-6588608"/>
+    <hyperlink ref="C61" location="'📤销售表'!A61" display="249-1402244-3486251"/>
     <hyperlink ref="B62" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C62" location="'📤销售表'!A62" display="249-2888479-8452654"/>
+    <hyperlink ref="C62" location="'📤销售表'!A60" display="503-2286952-6588608"/>
     <hyperlink ref="B63" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C63" location="'📤销售表'!A63" display="249-3209029-9999810"/>
+    <hyperlink ref="C63" location="'📤销售表'!A62" display="249-2888479-8452654"/>
     <hyperlink ref="B64" location="'📥进货表'!A18" display="3316423695109035788"/>
-    <hyperlink ref="C64" location="'📤销售表'!A65" display="503-8229948-4722203"/>
-    <hyperlink ref="B65" location="'📥进货表'!A19" display="3316454223181008960"/>
-    <hyperlink ref="C65" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="C64" location="'📤销售表'!A63" display="249-3209029-9999810"/>
+    <hyperlink ref="B65" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C65" location="'📤销售表'!A65" display="503-8229948-4722203"/>
+    <hyperlink ref="B66" location="'📥进货表'!A19" display="3316454223181008960"/>
+    <hyperlink ref="C66" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="C67" location="'📤销售表'!A67" display="503-9041299-9070211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -5174,25 +5174,76 @@
       </c>
       <c r="N67" s="27" t="n"/>
     </row>
-    <row r="68"/>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="25" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>46296</v>
+      </c>
+      <c r="D68" s="33" t="n">
+        <v>46300</v>
+      </c>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F68" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G68" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H68" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J68" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K68" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L68" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M68" s="25" t="inlineStr">
+        <is>
+          <t>250-1309729-4343820</t>
+        </is>
+      </c>
+      <c r="N68" s="27" t="n"/>
+    </row>
+    <row r="69"/>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 85,069</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>65 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 86,742</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>66 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="71"/>
     <row r="72"/>
     <row r="73"/>
@@ -5327,9 +5378,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="M69:N69"/>
-    <mergeCell ref="I69:L69"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="I70:L70"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5483,7 +5534,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>7.24</v>
@@ -5492,11 +5543,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (4个)</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5687,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8403,83 +8454,116 @@
       </c>
       <c r="B66" s="36" t="inlineStr">
         <is>
-          <t>3316454223181008960</t>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C66" s="36" t="inlineStr">
         <is>
-          <t>249-0470172-4818202</t>
+          <t>250-1309729-4343820</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E66" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F66" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="29" t="n">
-        <v>6.58</v>
+        <v>7.45</v>
       </c>
       <c r="H66" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="25" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="27" t="inlineStr">
+      <c r="B67" s="36" t="inlineStr">
+        <is>
+          <t>3316454223181008960</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>249-0470172-4818202</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="F67" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="29" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="H67" s="34" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="25" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
         <is>
           <t>（无）</t>
         </is>
       </c>
-      <c r="C67" s="36" t="inlineStr">
+      <c r="C68" s="36" t="inlineStr">
         <is>
           <t>503-9041299-9070211</t>
         </is>
       </c>
-      <c r="D67" s="27" t="inlineStr">
+      <c r="D68" s="27" t="inlineStr">
         <is>
           <t>蝶型低反発メモリー枕</t>
         </is>
       </c>
-      <c r="E67" s="27" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>紫色</t>
         </is>
       </c>
-      <c r="F67" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="29" t="n">
+      <c r="F68" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="34" t="n">
+      <c r="H68" s="34" t="n">
         <v>2443</v>
       </c>
     </row>
-    <row r="68"/>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="69"/>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G69" s="31" t="n">
-        <v>393.07</v>
-      </c>
-      <c r="H69" s="35" t="n">
-        <v>85069</v>
-      </c>
-    </row>
-    <row r="70"/>
+      <c r="G70" s="31" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="H70" s="35" t="n">
+        <v>86742</v>
+      </c>
+    </row>
     <row r="71"/>
     <row r="72"/>
     <row r="73"/>
@@ -8614,7 +8698,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8744,9 +8828,11 @@
     <hyperlink ref="C64" location="'📤销售表'!A63" display="249-3209029-9999810"/>
     <hyperlink ref="B65" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C65" location="'📤销售表'!A65" display="503-8229948-4722203"/>
-    <hyperlink ref="B66" location="'📥进货表'!A19" display="3316454223181008960"/>
-    <hyperlink ref="C66" location="'📤销售表'!A64" display="249-0470172-4818202"/>
-    <hyperlink ref="C67" location="'📤销售表'!A67" display="503-9041299-9070211"/>
+    <hyperlink ref="B66" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C66" location="'📤销售表'!A68" display="250-1309729-4343820"/>
+    <hyperlink ref="B67" location="'📥进货表'!A19" display="3316454223181008960"/>
+    <hyperlink ref="C67" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="C68" location="'📤销售表'!A67" display="503-9041299-9070211"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -5226,27 +5226,180 @@
       </c>
       <c r="N68" s="27" t="n"/>
     </row>
-    <row r="69"/>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D69" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E69" s="27" t="inlineStr">
+        <is>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
+        </is>
+      </c>
+      <c r="F69" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G69" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H69" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J69" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K69" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L69" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M69" s="25" t="inlineStr">
+        <is>
+          <t>249-4181340-2369468</t>
+        </is>
+      </c>
+      <c r="N69" s="27" t="n"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D70" s="33" t="n">
+        <v>46308</v>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="F70" s="27" t="inlineStr">
+        <is>
+          <t>粉色</t>
+        </is>
+      </c>
+      <c r="G70" s="25" t="inlineStr">
+        <is>
+          <t>YY-WNMI-ULH2</t>
+        </is>
+      </c>
+      <c r="H70" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="34" t="n">
+        <v>2888</v>
+      </c>
+      <c r="J70" s="34" t="n">
+        <v>263</v>
+      </c>
+      <c r="K70" s="34" t="n">
+        <v>445</v>
+      </c>
+      <c r="L70" s="34" t="n">
+        <v>2443</v>
+      </c>
+      <c r="M70" s="25" t="inlineStr">
+        <is>
+          <t>250-4243924-5379817</t>
+        </is>
+      </c>
+      <c r="N70" s="27" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D71" s="33" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="F71" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="G71" s="25" t="inlineStr">
+        <is>
+          <t>WD-FBTT-4QTJ</t>
+        </is>
+      </c>
+      <c r="H71" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="34" t="n">
+        <v>2888</v>
+      </c>
+      <c r="J71" s="34" t="n">
+        <v>263</v>
+      </c>
+      <c r="K71" s="34" t="n">
+        <v>445</v>
+      </c>
+      <c r="L71" s="34" t="n">
+        <v>2443</v>
+      </c>
+      <c r="M71" s="25" t="inlineStr">
+        <is>
+          <t>250-7290246-4027859</t>
+        </is>
+      </c>
+      <c r="N71" s="27" t="n"/>
+    </row>
+    <row r="72"/>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 86,742</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>66 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 93,301</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>69 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="74"/>
     <row r="75"/>
     <row r="76"/>
@@ -5378,9 +5531,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="I70:L70"/>
-    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="I73:L73"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5534,7 +5687,7 @@
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="29" t="n">
         <v>7.24</v>
@@ -5543,11 +5696,11 @@
         <v>46284.68633101852</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>库存充足 (2个)</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5840,7 @@
         </is>
       </c>
       <c r="D11" s="32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
@@ -8488,85 +8641,184 @@
       </c>
       <c r="B67" s="36" t="inlineStr">
         <is>
-          <t>3316454223181008960</t>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C67" s="36" t="inlineStr">
         <is>
-          <t>249-0470172-4818202</t>
+          <t>249-4181340-2369468</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>塑料除黄剂 黄ばみ除去剤</t>
         </is>
       </c>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F67" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="29" t="n">
-        <v>6.58</v>
+        <v>7.45</v>
       </c>
       <c r="H67" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="25" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="36" t="inlineStr">
+        <is>
+          <t>3316454223181008960</t>
+        </is>
+      </c>
+      <c r="C68" s="36" t="inlineStr">
+        <is>
+          <t>249-0470172-4818202</t>
+        </is>
+      </c>
+      <c r="D68" s="27" t="inlineStr">
+        <is>
+          <t>玻璃修复膏 50g 车用</t>
+        </is>
+      </c>
+      <c r="E68" s="27" t="inlineStr">
+        <is>
+          <t>50g</t>
+        </is>
+      </c>
+      <c r="F68" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="29" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="H68" s="34" t="n">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="25" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>（无）</t>
         </is>
       </c>
-      <c r="C68" s="36" t="inlineStr">
+      <c r="C69" s="36" t="inlineStr">
         <is>
           <t>503-9041299-9070211</t>
         </is>
       </c>
-      <c r="D68" s="27" t="inlineStr">
+      <c r="D69" s="27" t="inlineStr">
         <is>
           <t>蝶型低反発メモリー枕</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
+      <c r="E69" s="27" t="inlineStr">
         <is>
           <t>紫色</t>
         </is>
       </c>
-      <c r="F68" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="29" t="n">
+      <c r="F69" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="34" t="n">
+      <c r="H69" s="34" t="n">
         <v>2443</v>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="25" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C70" s="36" t="inlineStr">
+        <is>
+          <t>250-4243924-5379817</t>
+        </is>
+      </c>
+      <c r="D70" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="E70" s="27" t="inlineStr">
+        <is>
+          <t>粉色</t>
+        </is>
+      </c>
+      <c r="F70" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="34" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="25" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C71" s="36" t="inlineStr">
+        <is>
+          <t>250-7290246-4027859</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="F71" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="34" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="72"/>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G70" s="31" t="n">
-        <v>400.52</v>
-      </c>
-      <c r="H70" s="35" t="n">
-        <v>86742</v>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
+      <c r="G73" s="31" t="n">
+        <v>407.97</v>
+      </c>
+      <c r="H73" s="35" t="n">
+        <v>93301</v>
+      </c>
+    </row>
     <row r="74"/>
     <row r="75"/>
     <row r="76"/>
@@ -8698,7 +8950,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A73:E73"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -8830,9 +9082,13 @@
     <hyperlink ref="C65" location="'📤销售表'!A65" display="503-8229948-4722203"/>
     <hyperlink ref="B66" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C66" location="'📤销售表'!A68" display="250-1309729-4343820"/>
-    <hyperlink ref="B67" location="'📥进货表'!A19" display="3316454223181008960"/>
-    <hyperlink ref="C67" location="'📤销售表'!A64" display="249-0470172-4818202"/>
-    <hyperlink ref="C68" location="'📤销售表'!A67" display="503-9041299-9070211"/>
+    <hyperlink ref="B67" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C67" location="'📤销售表'!A69" display="249-4181340-2369468"/>
+    <hyperlink ref="B68" location="'📥进货表'!A19" display="3316454223181008960"/>
+    <hyperlink ref="C68" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="C69" location="'📤销售表'!A67" display="503-9041299-9070211"/>
+    <hyperlink ref="C70" location="'📤销售表'!A70" display="250-4243924-5379817"/>
+    <hyperlink ref="C71" location="'📤销售表'!A71" display="250-7290246-4027859"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -723,7 +723,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="41" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1483,24 +1483,106 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>46312.57342592593</v>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>粉色</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="H20" s="27" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
+        </is>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>28.32</v>
+      </c>
+      <c r="J20" s="27" t="inlineStr">
+        <is>
+          <t>蝶型记忆枕补货 粉色1个（销售单250-4243924-5379817）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>46312.57342592593</v>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="H21" s="27" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
+        </is>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="J21" s="27" t="inlineStr">
+        <is>
+          <t>蝶型记忆枕补货 紫色2个（销售单503-9041299-9070211、250-7290246-4027859）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G21" s="31" t="n">
-        <v>484.67</v>
-      </c>
-      <c r="H21" s="32" t="inlineStr">
-        <is>
-          <t>17 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+      <c r="G23" s="31" t="n">
+        <v>569.67</v>
+      </c>
+      <c r="H23" s="32" t="inlineStr">
+        <is>
+          <t>19 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
@@ -1682,9 +1764,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5832,23 +5914,54 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>粉色</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>46312.57342592593</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D12" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>7 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>8 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15"/>
@@ -6041,8 +6154,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E12:H12"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8707,14 +8820,14 @@
       <c r="A69" s="25" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B69" s="36" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
         </is>
       </c>
       <c r="C69" s="36" t="inlineStr">
         <is>
-          <t>503-9041299-9070211</t>
+          <t>250-4243924-5379817</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
@@ -8724,14 +8837,14 @@
       </c>
       <c r="E69" s="27" t="inlineStr">
         <is>
-          <t>紫色</t>
+          <t>粉色</t>
         </is>
       </c>
       <c r="F69" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="29" t="n">
-        <v>0</v>
+        <v>28.32</v>
       </c>
       <c r="H69" s="34" t="n">
         <v>2443</v>
@@ -8741,14 +8854,14 @@
       <c r="A70" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B70" s="36" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
         </is>
       </c>
       <c r="C70" s="36" t="inlineStr">
         <is>
-          <t>250-4243924-5379817</t>
+          <t>503-9041299-9070211</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
@@ -8758,14 +8871,14 @@
       </c>
       <c r="E70" s="27" t="inlineStr">
         <is>
-          <t>粉色</t>
+          <t>紫色</t>
         </is>
       </c>
       <c r="F70" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="29" t="n">
-        <v>0</v>
+        <v>28.34</v>
       </c>
       <c r="H70" s="34" t="n">
         <v>2443</v>
@@ -8775,9 +8888,9 @@
       <c r="A71" s="25" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
         </is>
       </c>
       <c r="C71" s="36" t="inlineStr">
@@ -8799,7 +8912,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="29" t="n">
-        <v>0</v>
+        <v>28.34</v>
       </c>
       <c r="H71" s="34" t="n">
         <v>2443</v>
@@ -8813,7 +8926,7 @@
         </is>
       </c>
       <c r="G73" s="31" t="n">
-        <v>407.97</v>
+        <v>492.97</v>
       </c>
       <c r="H73" s="35" t="n">
         <v>93301</v>
@@ -9086,8 +9199,11 @@
     <hyperlink ref="C67" location="'📤销售表'!A69" display="249-4181340-2369468"/>
     <hyperlink ref="B68" location="'📥进货表'!A19" display="3316454223181008960"/>
     <hyperlink ref="C68" location="'📤销售表'!A64" display="249-0470172-4818202"/>
-    <hyperlink ref="C69" location="'📤销售表'!A67" display="503-9041299-9070211"/>
-    <hyperlink ref="C70" location="'📤销售表'!A70" display="250-4243924-5379817"/>
+    <hyperlink ref="B69" location="'📥进货表'!A20" display="3316962145004008960"/>
+    <hyperlink ref="C69" location="'📤销售表'!A70" display="250-4243924-5379817"/>
+    <hyperlink ref="B70" location="'📥进货表'!A21" display="3316962145004008960"/>
+    <hyperlink ref="C70" location="'📤销售表'!A67" display="503-9041299-9070211"/>
+    <hyperlink ref="B71" location="'📥进货表'!A21" display="3316962145004008960"/>
     <hyperlink ref="C71" location="'📤销售表'!A71" display="250-7290246-4027859"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📥进货表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📤销售表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="📦库存表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="❌库存遗失表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="🔗关联视图" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📥进货表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📤销售表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📦库存表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="❌库存遗失表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔗关联视图" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1785,7 +1785,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
@@ -5464,26 +5464,128 @@
       </c>
       <c r="N71" s="27" t="n"/>
     </row>
-    <row r="72"/>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D72" s="33" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
+        </is>
+      </c>
+      <c r="F72" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G72" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H72" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J72" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K72" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L72" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M72" s="25" t="inlineStr">
+        <is>
+          <t>249-7161377-1807051</t>
+        </is>
+      </c>
+      <c r="N72" s="27" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D73" s="33" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
+        </is>
+      </c>
+      <c r="F73" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G73" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H73" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J73" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K73" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L73" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M73" s="25" t="inlineStr">
+        <is>
+          <t>249-6762901-5951851</t>
+        </is>
+      </c>
+      <c r="N73" s="27" t="n"/>
+    </row>
+    <row r="74"/>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 93,301</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>69 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75"/>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 96,647</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>71 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="76"/>
     <row r="77"/>
     <row r="78"/>
@@ -5613,9 +5715,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="I73:L73"/>
+    <mergeCell ref="I75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="A75:D75"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5760,29 +5862,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>7.24</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46304</v>
+        <v>46214</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (2个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -5792,25 +5894,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46221.59108796297</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -5824,25 +5926,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>20</v>
+        <v>7.24</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46221</v>
+        <v>46315</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -5954,7 +6056,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
@@ -6516,7 +6618,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
@@ -8788,32 +8890,32 @@
       </c>
       <c r="B68" s="36" t="inlineStr">
         <is>
-          <t>3316454223181008960</t>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C68" s="36" t="inlineStr">
         <is>
-          <t>249-0470172-4818202</t>
+          <t>249-7161377-1807051</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr">
         <is>
-          <t>玻璃修复膏 50g 车用</t>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
         </is>
       </c>
       <c r="E68" s="27" t="inlineStr">
         <is>
-          <t>50g</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F68" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="29" t="n">
-        <v>6.58</v>
+        <v>7.45</v>
       </c>
       <c r="H68" s="34" t="n">
-        <v>1005</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
@@ -8822,32 +8924,32 @@
       </c>
       <c r="B69" s="36" t="inlineStr">
         <is>
-          <t>3316962145004008960</t>
+          <t>3316423695109035788</t>
         </is>
       </c>
       <c r="C69" s="36" t="inlineStr">
         <is>
-          <t>250-4243924-5379817</t>
+          <t>249-6762901-5951851</t>
         </is>
       </c>
       <c r="D69" s="27" t="inlineStr">
         <is>
-          <t>蝶型低反発メモリー枕</t>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
         </is>
       </c>
       <c r="E69" s="27" t="inlineStr">
         <is>
-          <t>粉色</t>
+          <t>100ml</t>
         </is>
       </c>
       <c r="F69" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="29" t="n">
-        <v>28.32</v>
+        <v>7.45</v>
       </c>
       <c r="H69" s="34" t="n">
-        <v>2443</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1">
@@ -8856,32 +8958,32 @@
       </c>
       <c r="B70" s="36" t="inlineStr">
         <is>
-          <t>3316962145004008960</t>
+          <t>3316454223181008960</t>
         </is>
       </c>
       <c r="C70" s="36" t="inlineStr">
         <is>
-          <t>503-9041299-9070211</t>
+          <t>249-0470172-4818202</t>
         </is>
       </c>
       <c r="D70" s="27" t="inlineStr">
         <is>
-          <t>蝶型低反発メモリー枕</t>
+          <t>玻璃修复膏 50g 车用</t>
         </is>
       </c>
       <c r="E70" s="27" t="inlineStr">
         <is>
-          <t>紫色</t>
+          <t>50g</t>
         </is>
       </c>
       <c r="F70" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="29" t="n">
-        <v>28.34</v>
+        <v>6.58</v>
       </c>
       <c r="H70" s="34" t="n">
-        <v>2443</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1">
@@ -8895,7 +8997,7 @@
       </c>
       <c r="C71" s="36" t="inlineStr">
         <is>
-          <t>250-7290246-4027859</t>
+          <t>250-4243924-5379817</t>
         </is>
       </c>
       <c r="D71" s="27" t="inlineStr">
@@ -8905,35 +9007,101 @@
       </c>
       <c r="E71" s="27" t="inlineStr">
         <is>
-          <t>紫色</t>
+          <t>粉色</t>
         </is>
       </c>
       <c r="F71" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="29" t="n">
-        <v>28.34</v>
+        <v>28.32</v>
       </c>
       <c r="H71" s="34" t="n">
         <v>2443</v>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="30" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="36" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
+        </is>
+      </c>
+      <c r="C72" s="36" t="inlineStr">
+        <is>
+          <t>503-9041299-9070211</t>
+        </is>
+      </c>
+      <c r="D72" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="E72" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="F72" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="29" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="H72" s="34" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="36" t="inlineStr">
+        <is>
+          <t>3316962145004008960</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>250-7290246-4027859</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>蝶型低反発メモリー枕</t>
+        </is>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="F73" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="29" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="H73" s="34" t="n">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G73" s="31" t="n">
-        <v>492.97</v>
-      </c>
-      <c r="H73" s="35" t="n">
-        <v>93301</v>
-      </c>
-    </row>
-    <row r="74"/>
-    <row r="75"/>
+      <c r="G75" s="31" t="n">
+        <v>507.87</v>
+      </c>
+      <c r="H75" s="35" t="n">
+        <v>96647</v>
+      </c>
+    </row>
     <row r="76"/>
     <row r="77"/>
     <row r="78"/>
@@ -9063,7 +9231,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A75:E75"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -9197,14 +9365,18 @@
     <hyperlink ref="C66" location="'📤销售表'!A68" display="250-1309729-4343820"/>
     <hyperlink ref="B67" location="'📥进货表'!A18" display="3316423695109035788"/>
     <hyperlink ref="C67" location="'📤销售表'!A69" display="249-4181340-2369468"/>
-    <hyperlink ref="B68" location="'📥进货表'!A19" display="3316454223181008960"/>
-    <hyperlink ref="C68" location="'📤销售表'!A64" display="249-0470172-4818202"/>
-    <hyperlink ref="B69" location="'📥进货表'!A20" display="3316962145004008960"/>
-    <hyperlink ref="C69" location="'📤销售表'!A70" display="250-4243924-5379817"/>
-    <hyperlink ref="B70" location="'📥进货表'!A21" display="3316962145004008960"/>
-    <hyperlink ref="C70" location="'📤销售表'!A67" display="503-9041299-9070211"/>
-    <hyperlink ref="B71" location="'📥进货表'!A21" display="3316962145004008960"/>
-    <hyperlink ref="C71" location="'📤销售表'!A71" display="250-7290246-4027859"/>
+    <hyperlink ref="B68" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C68" location="'📤销售表'!A72" display="249-7161377-1807051"/>
+    <hyperlink ref="B69" location="'📥进货表'!A18" display="3316423695109035788"/>
+    <hyperlink ref="C69" location="'📤销售表'!A73" display="249-6762901-5951851"/>
+    <hyperlink ref="B70" location="'📥进货表'!A19" display="3316454223181008960"/>
+    <hyperlink ref="C70" location="'📤销售表'!A64" display="249-0470172-4818202"/>
+    <hyperlink ref="B71" location="'📥进货表'!A20" display="3316962145004008960"/>
+    <hyperlink ref="C71" location="'📤销售表'!A70" display="250-4243924-5379817"/>
+    <hyperlink ref="B72" location="'📥进货表'!A21" display="3316962145004008960"/>
+    <hyperlink ref="C72" location="'📤销售表'!A67" display="503-9041299-9070211"/>
+    <hyperlink ref="B73" location="'📥进货表'!A21" display="3316962145004008960"/>
+    <hyperlink ref="C73" location="'📤销售表'!A71" display="250-7290246-4027859"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -715,7 +715,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
@@ -1567,23 +1567,64 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>抖音商城</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>46319.56798611111</v>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>500ml琥珀圆形大力神杯（牛皮纸盒包装）</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="29" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="H22" s="27" t="inlineStr">
+        <is>
+          <t>6930757232179314364</t>
+        </is>
+      </c>
+      <c r="I22" s="29" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="J22" s="27" t="inlineStr">
+        <is>
+          <t>大力神杯琥珀色补货（SKU LK-RN2M-G3YX；原价29.04-优惠3.48）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G23" s="31" t="n">
-        <v>569.67</v>
-      </c>
-      <c r="H23" s="32" t="inlineStr">
-        <is>
-          <t>19 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="G24" s="31" t="n">
+        <v>595.23</v>
+      </c>
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>20 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -1765,8 +1806,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5568,25 +5609,76 @@
       </c>
       <c r="N73" s="27" t="n"/>
     </row>
-    <row r="74"/>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="D74" s="33" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="F74" s="27" t="inlineStr">
+        <is>
+          <t>琥珀色</t>
+        </is>
+      </c>
+      <c r="G74" s="25" t="inlineStr">
+        <is>
+          <t>LK-RN2M-G3YX</t>
+        </is>
+      </c>
+      <c r="H74" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J74" s="34" t="n">
+        <v>184</v>
+      </c>
+      <c r="K74" s="34" t="n">
+        <v>312</v>
+      </c>
+      <c r="L74" s="34" t="n">
+        <v>1714</v>
+      </c>
+      <c r="M74" s="25" t="inlineStr">
+        <is>
+          <t>249-4292688-0355859</t>
+        </is>
+      </c>
+      <c r="N74" s="27" t="n"/>
+    </row>
+    <row r="75"/>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 96,647</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>71 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="76"/>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 98,361</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>72 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
@@ -5715,9 +5807,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="I76:L76"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5906,13 +5998,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>20</v>
+        <v>22.78</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46221.59108796297</v>
+        <v>46319.56798611111</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46221</v>
+        <v>46319</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -6719,7 +6811,7 @@
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>249-6387958-2579060</t>
+          <t>249-4292688-0355859</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -9088,21 +9180,54 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="36" t="inlineStr">
+        <is>
+          <t>6930757232179314364</t>
+        </is>
+      </c>
+      <c r="C74" s="36" t="inlineStr">
+        <is>
+          <t>249-6387958-2579060</t>
+        </is>
+      </c>
+      <c r="D74" s="27" t="inlineStr">
+        <is>
+          <t>500ml啤酒杯耐热耐冷足球奖杯杯</t>
+        </is>
+      </c>
+      <c r="E74" s="27" t="inlineStr">
+        <is>
+          <t>琥珀色</t>
+        </is>
+      </c>
+      <c r="F74" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="29" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="H74" s="34" t="n">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G75" s="31" t="n">
-        <v>507.87</v>
-      </c>
-      <c r="H75" s="35" t="n">
-        <v>96647</v>
-      </c>
-    </row>
-    <row r="76"/>
+      <c r="G76" s="31" t="n">
+        <v>533.4299999999999</v>
+      </c>
+      <c r="H76" s="35" t="n">
+        <v>98361</v>
+      </c>
+    </row>
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
@@ -9231,14 +9356,14 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" location="'📥进货表'!A3" display="3311879379799327755"/>
     <hyperlink ref="C3" location="'📤销售表'!A3" display="503-95444475-5097463"/>
     <hyperlink ref="B4" location="'📥进货表'!A4" display="260718-641864876461684"/>
-    <hyperlink ref="C4" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="C4" location="'📤销售表'!A74" display="249-4292688-0355859"/>
     <hyperlink ref="B5" location="'📥进货表'!A5" display="3314711712867008960"/>
     <hyperlink ref="C5" location="'📤销售表'!A5" display="249-4866874-7926210"/>
     <hyperlink ref="B6" location="'📥进货表'!A5" display="3314711712867008960"/>
@@ -9377,6 +9502,8 @@
     <hyperlink ref="C72" location="'📤销售表'!A67" display="503-9041299-9070211"/>
     <hyperlink ref="B73" location="'📥进货表'!A21" display="3316962145004008960"/>
     <hyperlink ref="C73" location="'📤销售表'!A71" display="250-7290246-4027859"/>
+    <hyperlink ref="B74" location="'📥进货表'!A22" display="6930757232179314364"/>
+    <hyperlink ref="C74" location="'📤销售表'!A4" display="249-6387958-2579060"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1609,23 +1609,64 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>46321.64201388889</v>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>宠物耳螨油SON082</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>耳部清洁液22.2ml</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>3316531515120054152</t>
+        </is>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>猫犬耳洗浄液/耳螨油补货（单价2.17×3-优惠1.00）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G24" s="31" t="n">
-        <v>595.23</v>
-      </c>
-      <c r="H24" s="32" t="inlineStr">
-        <is>
-          <t>20 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="G25" s="31" t="n">
+        <v>601.73</v>
+      </c>
+      <c r="H25" s="32" t="inlineStr">
+        <is>
+          <t>21 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -1806,8 +1847,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1826,11 +1867,11 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -5661,26 +5702,128 @@
       </c>
       <c r="N74" s="27" t="n"/>
     </row>
-    <row r="75"/>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>46319</v>
+      </c>
+      <c r="D75" s="33" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E75" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="F75" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="G75" s="25" t="inlineStr">
+        <is>
+          <t>EE-32N2-DON3</t>
+        </is>
+      </c>
+      <c r="H75" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="34" t="n">
+        <v>656</v>
+      </c>
+      <c r="J75" s="34" t="n">
+        <v>60</v>
+      </c>
+      <c r="K75" s="34" t="n">
+        <v>89</v>
+      </c>
+      <c r="L75" s="34" t="n">
+        <v>966</v>
+      </c>
+      <c r="M75" s="25" t="inlineStr">
+        <is>
+          <t>250-0438506-0738236</t>
+        </is>
+      </c>
+      <c r="N75" s="27" t="n"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D76" s="33" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="F76" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="G76" s="25" t="inlineStr">
+        <is>
+          <t>16-5R3P-9HTQ</t>
+        </is>
+      </c>
+      <c r="H76" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="34" t="n">
+        <v>999</v>
+      </c>
+      <c r="J76" s="34" t="n">
+        <v>91</v>
+      </c>
+      <c r="K76" s="34" t="n">
+        <v>117</v>
+      </c>
+      <c r="L76" s="34" t="n">
+        <v>1281</v>
+      </c>
+      <c r="M76" s="25" t="inlineStr">
+        <is>
+          <t>249-0515593-2298202</t>
+        </is>
+      </c>
+      <c r="N76" s="27" t="n"/>
+    </row>
+    <row r="77"/>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 98,361</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>72 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78"/>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 100,608</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>74 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
@@ -5807,9 +5950,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="I76:L76"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="A78:D78"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5954,29 +6097,27 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>宠物耳螨油SON082</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>耳部清洁液22.2ml</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>2.17</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>46214</v>
-      </c>
+        <v>46321.64201388889</v>
+      </c>
+      <c r="G5" s="25" t="n"/>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (3个)</t>
         </is>
       </c>
     </row>
@@ -5986,25 +6127,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>22.78</v>
+        <v>5.9</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46319.56798611111</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46319</v>
+        <v>46214</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -6018,25 +6159,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>7.24</v>
+        <v>22.78</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46319.56798611111</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46315</v>
+        <v>46319</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -6050,25 +6191,25 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>4個セット(黄色2+灰色2)</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>4</v>
+        <v>7.24</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>46259</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>46259</v>
+        <v>46315</v>
       </c>
       <c r="H8" s="27" t="inlineStr">
         <is>
@@ -6082,25 +6223,25 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>韩伦美羽烟酰胺炫白牙膏</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>4個セット(黄色2+灰色2)</t>
         </is>
       </c>
       <c r="D9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
@@ -6114,49 +6255,80 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>跨境卷装牛角记忆睡眠枕头</t>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>粉色</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="D10" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>46274</v>
+      </c>
+      <c r="G10" s="33" t="n">
+        <v>46272</v>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>粉色</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="29" t="n">
         <v>28.33</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F11" s="33" t="n">
         <v>46312.57342592593</v>
       </c>
-      <c r="G10" s="33" t="n">
+      <c r="G11" s="33" t="n">
         <v>46307</v>
       </c>
-      <c r="H10" s="27" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>已售罄</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>📊 库存合计</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>8 种商品</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+      <c r="D13" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>9 种商品</t>
+        </is>
+      </c>
+    </row>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
@@ -6348,8 +6520,8 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E13:H13"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6710,8 +6882,8 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -9214,22 +9386,88 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C75" s="36" t="inlineStr">
+        <is>
+          <t>250-0438506-0738236</t>
+        </is>
+      </c>
+      <c r="D75" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="E75" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="F75" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="34" t="n">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C76" s="36" t="inlineStr">
+        <is>
+          <t>249-0515593-2298202</t>
+        </is>
+      </c>
+      <c r="D76" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="E76" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="F76" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="34" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G76" s="31" t="n">
+      <c r="G78" s="31" t="n">
         <v>533.4299999999999</v>
       </c>
-      <c r="H76" s="35" t="n">
-        <v>98361</v>
-      </c>
-    </row>
-    <row r="77"/>
-    <row r="78"/>
+      <c r="H78" s="35" t="n">
+        <v>100608</v>
+      </c>
+    </row>
     <row r="79"/>
     <row r="80"/>
     <row r="81"/>
@@ -9356,7 +9594,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A78:E78"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -9504,6 +9742,8 @@
     <hyperlink ref="C73" location="'📤销售表'!A71" display="250-7290246-4027859"/>
     <hyperlink ref="B74" location="'📥进货表'!A22" display="6930757232179314364"/>
     <hyperlink ref="C74" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="C75" location="'📤销售表'!A75" display="250-0438506-0738236"/>
+    <hyperlink ref="C76" location="'📤销售表'!A76" display="249-0515593-2298202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -5806,26 +5806,128 @@
       </c>
       <c r="N76" s="27" t="n"/>
     </row>
-    <row r="77"/>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="30" t="inlineStr">
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D77" s="33" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E77" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="F77" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="G77" s="25" t="inlineStr">
+        <is>
+          <t>16-5R3P-9HTQ</t>
+        </is>
+      </c>
+      <c r="H77" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="34" t="n">
+        <v>999</v>
+      </c>
+      <c r="J77" s="34" t="n">
+        <v>91</v>
+      </c>
+      <c r="K77" s="34" t="n">
+        <v>117</v>
+      </c>
+      <c r="L77" s="34" t="n">
+        <v>1281</v>
+      </c>
+      <c r="M77" s="25" t="inlineStr">
+        <is>
+          <t>503-4832456-8143020</t>
+        </is>
+      </c>
+      <c r="N77" s="27" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Amazon日本站</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D78" s="33" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
+        </is>
+      </c>
+      <c r="F78" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="inlineStr">
+        <is>
+          <t>asd159</t>
+        </is>
+      </c>
+      <c r="H78" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="34" t="n">
+        <v>1468</v>
+      </c>
+      <c r="J78" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="K78" s="34" t="n">
+        <v>194</v>
+      </c>
+      <c r="L78" s="34" t="n">
+        <v>1673</v>
+      </c>
+      <c r="M78" s="25" t="inlineStr">
+        <is>
+          <t>249-1477564-5737434</t>
+        </is>
+      </c>
+      <c r="N78" s="27" t="n"/>
+    </row>
+    <row r="79"/>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>总销售额: JPY 100,608</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>74 笔销售</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80"/>
+      <c r="I80" s="32" t="inlineStr">
+        <is>
+          <t>总销售额: JPY 103,562</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>76 笔销售</t>
+        </is>
+      </c>
+    </row>
     <row r="81"/>
     <row r="82"/>
     <row r="83"/>
@@ -5950,9 +6052,9 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="I78:L78"/>
-    <mergeCell ref="A78:D78"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="I80:L80"/>
+    <mergeCell ref="M80:N80"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9454,22 +9556,88 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="30" t="inlineStr">
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>503-4832456-8143020</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 猫犬 ミミダニ 対策 耳洗浄液 22.2ml x 2本セット</t>
+        </is>
+      </c>
+      <c r="E77" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml×2本</t>
+        </is>
+      </c>
+      <c r="F77" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="34" t="n">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>（无）</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="inlineStr">
+        <is>
+          <t>249-1477564-5737434</t>
+        </is>
+      </c>
+      <c r="D78" s="27" t="inlineStr">
+        <is>
+          <t>プラスチック黄ばみ除去剤 イエローリノベーター</t>
+        </is>
+      </c>
+      <c r="E78" s="27" t="inlineStr">
+        <is>
+          <t>100ml</t>
+        </is>
+      </c>
+      <c r="F78" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="34" t="n">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G78" s="31" t="n">
+      <c r="G80" s="31" t="n">
         <v>533.4299999999999</v>
       </c>
-      <c r="H78" s="35" t="n">
-        <v>100608</v>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80"/>
+      <c r="H80" s="35" t="n">
+        <v>103562</v>
+      </c>
+    </row>
     <row r="81"/>
     <row r="82"/>
     <row r="83"/>
@@ -9594,7 +9762,7 @@
     <row r="202"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
@@ -9744,6 +9912,8 @@
     <hyperlink ref="C74" location="'📤销售表'!A4" display="249-6387958-2579060"/>
     <hyperlink ref="C75" location="'📤销售表'!A75" display="250-0438506-0738236"/>
     <hyperlink ref="C76" location="'📤销售表'!A76" display="249-0515593-2298202"/>
+    <hyperlink ref="C77" location="'📤销售表'!A77" display="503-4832456-8143020"/>
+    <hyperlink ref="C78" location="'📤销售表'!A78" display="249-1477564-5737434"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -717,7 +717,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>宠物耳螨油SON082</t>
+          <t>イヤークリーナー 耳洗浄液（宠物耳螨油SON082）</t>
         </is>
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>耳部清洁液22.2ml</t>
+          <t>22.2ml/瓶</t>
         </is>
       </c>
       <c r="F23" s="28" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="J23" s="27" t="inlineStr">
         <is>
-          <t>猫犬耳洗浄液/耳螨油补货（单价2.17×3-优惠1.00）</t>
+          <t>猫犬耳洗浄液3瓶（单价2.17×3-优惠1.00）；对应销售SKU EE-32N2-DON3/16-5R3P-9HTQ</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="F75" s="27" t="inlineStr">
         <is>
-          <t>22.2ml×2本</t>
+          <t>22.2ml×1本</t>
         </is>
       </c>
       <c r="G75" s="25" t="inlineStr">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="H76" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="34" t="n">
         <v>999</v>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="H77" s="28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" s="34" t="n">
         <v>999</v>
@@ -6071,7 +6071,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
     <col width="41" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -6199,27 +6199,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>宠物耳螨油SON082</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>耳部清洁液22.2ml</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>2.17</v>
+        <v>5.9</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46321.64201388889</v>
-      </c>
-      <c r="G5" s="25" t="n"/>
+        <v>46215.5080787037</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <v>46214</v>
+      </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (3个)</t>
+          <t>已售罄</t>
         </is>
       </c>
     </row>
@@ -6229,25 +6231,25 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>5.9</v>
+        <v>22.78</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46319.56798611111</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46214</v>
+        <v>46319</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
@@ -6261,25 +6263,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>22.78</v>
+        <v>7.24</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46319.56798611111</v>
+        <v>46284.68633101852</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46319</v>
+        <v>46315</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -6293,25 +6295,25 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>4個セット(黄色2+灰色2)</t>
         </is>
       </c>
       <c r="D8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>7.24</v>
+        <v>4</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46259</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>46315</v>
+        <v>46259</v>
       </c>
       <c r="H8" s="27" t="inlineStr">
         <is>
@@ -6325,25 +6327,25 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>4個セット(黄色2+灰色2)</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="D9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>46259</v>
+        <v>46274</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>46259</v>
+        <v>46272</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
@@ -6357,25 +6359,25 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>韩伦美羽烟酰胺炫白牙膏</t>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>粉色</t>
         </is>
       </c>
       <c r="D10" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>3</v>
+        <v>28.33</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>46274</v>
+        <v>46312.57342592593</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>46272</v>
+        <v>46307</v>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
@@ -6389,25 +6391,25 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>跨境卷装牛角记忆睡眠枕头</t>
+          <t>イヤークリーナー 耳洗浄液（宠物耳螨油SON082）</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>粉色</t>
+          <t>22.2ml/瓶</t>
         </is>
       </c>
       <c r="D11" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>28.33</v>
+        <v>2.17</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>46312.57342592593</v>
+        <v>46321.64201388889</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>46307</v>
+        <v>46320</v>
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
@@ -6423,7 +6425,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
@@ -9492,9 +9494,9 @@
       <c r="A75" s="25" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B75" s="36" t="inlineStr">
+        <is>
+          <t>3316531515120054152</t>
         </is>
       </c>
       <c r="C75" s="36" t="inlineStr">
@@ -9509,14 +9511,14 @@
       </c>
       <c r="E75" s="27" t="inlineStr">
         <is>
-          <t>22.2ml×2本</t>
+          <t>22.2ml×1本</t>
         </is>
       </c>
       <c r="F75" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="H75" s="34" t="n">
         <v>966</v>
@@ -9526,9 +9528,9 @@
       <c r="A76" s="25" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B76" s="36" t="inlineStr">
+        <is>
+          <t>3316531515120054152</t>
         </is>
       </c>
       <c r="C76" s="36" t="inlineStr">
@@ -9547,10 +9549,10 @@
         </is>
       </c>
       <c r="F76" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="H76" s="34" t="n">
         <v>1281</v>
@@ -9581,7 +9583,7 @@
         </is>
       </c>
       <c r="F77" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G77" s="29" t="n">
         <v>0</v>
@@ -9632,7 +9634,7 @@
         </is>
       </c>
       <c r="G80" s="31" t="n">
-        <v>533.4299999999999</v>
+        <v>539.9299999999999</v>
       </c>
       <c r="H80" s="35" t="n">
         <v>103562</v>
@@ -9910,7 +9912,9 @@
     <hyperlink ref="C73" location="'📤销售表'!A71" display="250-7290246-4027859"/>
     <hyperlink ref="B74" location="'📥进货表'!A22" display="6930757232179314364"/>
     <hyperlink ref="C74" location="'📤销售表'!A4" display="249-6387958-2579060"/>
+    <hyperlink ref="B75" location="'📥进货表'!A23" display="3316531515120054152"/>
     <hyperlink ref="C75" location="'📤销售表'!A75" display="250-0438506-0738236"/>
+    <hyperlink ref="B76" location="'📥进货表'!A23" display="3316531515120054152"/>
     <hyperlink ref="C76" location="'📤销售表'!A76" display="249-0515593-2298202"/>
     <hyperlink ref="C77" location="'📤销售表'!A77" display="503-4832456-8143020"/>
     <hyperlink ref="C78" location="'📤销售表'!A78" display="249-1477564-5737434"/>

--- a/购买记录/归档表格/购买记录_2026.xlsx
+++ b/购买记录/归档表格/购买记录_2026.xlsx
@@ -1651,24 +1651,106 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>46324.35577546297</v>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>イヤークリーナー 耳洗浄液（宠物耳螨油SON082）</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>22.2ml/瓶</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="29" t="n">
+        <v>29</v>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>3316549190024008960</t>
+        </is>
+      </c>
+      <c r="I24" s="29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" s="27" t="inlineStr">
+        <is>
+          <t>补货10瓶（单价2.50×10，无优惠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>46324.35799768518</v>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>KineShineX塑料除黄剂</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>100ml+毛巾</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="29" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H25" s="27" t="inlineStr">
+        <is>
+          <t>3316533999026090162</t>
+        </is>
+      </c>
+      <c r="I25" s="29" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J25" s="27" t="inlineStr">
+        <is>
+          <t>补货10个（单价6.50×10，无优惠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>📊 合计</t>
         </is>
       </c>
-      <c r="G25" s="31" t="n">
-        <v>601.73</v>
-      </c>
-      <c r="H25" s="32" t="inlineStr">
-        <is>
-          <t>21 笔进货</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
+      <c r="G27" s="31" t="n">
+        <v>705.23</v>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>23 笔进货</t>
+        </is>
+      </c>
+    </row>
     <row r="28"/>
     <row r="29"/>
     <row r="30"/>
@@ -1847,8 +1929,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="H27:J27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6135,29 +6217,29 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>KineShineX玻璃修复膏</t>
+          <t>KineShineX塑料除黄剂</t>
         </is>
       </c>
       <c r="C3" s="27" t="inlineStr">
         <is>
-          <t>50g+海绵</t>
+          <t>100ml+毛巾</t>
         </is>
       </c>
       <c r="D3" s="28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>6.33</v>
+        <v>7.29</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>46293</v>
+        <v>46324.35799768518</v>
       </c>
       <c r="G3" s="33" t="n">
-        <v>46289</v>
+        <v>46323</v>
       </c>
       <c r="H3" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (9个)</t>
         </is>
       </c>
     </row>
@@ -6167,29 +6249,29 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>多功能不锈钢压蒜器</t>
+          <t>イヤークリーナー 耳洗浄液（宠物耳螨油SON082）</t>
         </is>
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>按压式2个装 绿色</t>
+          <t>22.2ml/瓶</t>
         </is>
       </c>
       <c r="D4" s="28" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>4.61</v>
+        <v>2.73</v>
       </c>
       <c r="F4" s="33" t="n">
-        <v>46270</v>
+        <v>46324.35577546297</v>
       </c>
       <c r="G4" s="33" t="n">
-        <v>46295</v>
+        <v>46321</v>
       </c>
       <c r="H4" s="27" t="inlineStr">
         <is>
-          <t>库存充足 (5个)</t>
+          <t>库存充足 (8个)</t>
         </is>
       </c>
     </row>
@@ -6199,29 +6281,29 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>创意世界杯足球大力神杯</t>
+          <t>KineShineX玻璃修复膏</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
+          <t>50g+海绵</t>
         </is>
       </c>
       <c r="D5" s="28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>5.9</v>
+        <v>6.33</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>46215.5080787037</v>
+        <v>46293</v>
       </c>
       <c r="G5" s="33" t="n">
-        <v>46214</v>
+        <v>46289</v>
       </c>
       <c r="H5" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -6231,29 +6313,29 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
+          <t>多功能不锈钢压蒜器</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
+          <t>按压式2个装 绿色</t>
         </is>
       </c>
       <c r="D6" s="28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>22.78</v>
+        <v>4.61</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>46319.56798611111</v>
+        <v>46270</v>
       </c>
       <c r="G6" s="33" t="n">
-        <v>46319</v>
+        <v>46295</v>
       </c>
       <c r="H6" s="27" t="inlineStr">
         <is>
-          <t>已售罄</t>
+          <t>库存充足 (5个)</t>
         </is>
       </c>
     </row>
@@ -6263,25 +6345,25 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>KineShineX塑料除黄剂</t>
+          <t>创意世界杯足球大力神杯</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>100ml+毛巾</t>
+          <t>500ml透明圆形足球杯(牛皮纸盒包装)</t>
         </is>
       </c>
       <c r="D7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>7.24</v>
+        <v>5.9</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>46284.68633101852</v>
+        <v>46215.5080787037</v>
       </c>
       <c r="G7" s="33" t="n">
-        <v>46315</v>
+        <v>46214</v>
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
@@ -6295,25 +6377,25 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>多功能清洁棉海绵吸水海绵</t>
+          <t>创意大力神杯世界杯足球玻璃啤酒杯</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>4個セット(黄色2+灰色2)</t>
+          <t>500ML电镀圆球形大力神杯（牛皮纸盒包装）</t>
         </is>
       </c>
       <c r="D8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>4</v>
+        <v>22.78</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>46259</v>
+        <v>46319.56798611111</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>46259</v>
+        <v>46319</v>
       </c>
       <c r="H8" s="27" t="inlineStr">
         <is>
@@ -6327,25 +6409,25 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>韩伦美羽烟酰胺炫白牙膏</t>
+          <t>多功能清洁棉海绵吸水海绵</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>100g</t>
+          <t>4個セット(黄色2+灰色2)</t>
         </is>
       </c>
       <c r="D9" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="G9" s="33" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
@@ -6359,25 +6441,25 @@
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>跨境卷装牛角记忆睡眠枕头</t>
+          <t>韩伦美羽烟酰胺炫白牙膏</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>粉色</t>
+          <t>100g</t>
         </is>
       </c>
       <c r="D10" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>28.33</v>
+        <v>3</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>46312.57342592593</v>
+        <v>46274</v>
       </c>
       <c r="G10" s="33" t="n">
-        <v>46307</v>
+        <v>46272</v>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
@@ -6391,25 +6473,25 @@
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>イヤークリーナー 耳洗浄液（宠物耳螨油SON082）</t>
+          <t>跨境卷装牛角记忆睡眠枕头</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>22.2ml/瓶</t>
+          <t>粉色</t>
         </is>
       </c>
       <c r="D11" s="28" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>2.17</v>
+        <v>28.33</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>46321.64201388889</v>
+        <v>46312.57342592593</v>
       </c>
       <c r="G11" s="33" t="n">
-        <v>46320</v>
+        <v>46307</v>
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
@@ -6425,7 +6507,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
@@ -9562,9 +9644,9 @@
       <c r="A77" s="25" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>3316549190024008960</t>
         </is>
       </c>
       <c r="C77" s="36" t="inlineStr">
@@ -9586,7 +9668,7 @@
         <v>2</v>
       </c>
       <c r="G77" s="29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="H77" s="34" t="n">
         <v>1281</v>
@@ -9596,9 +9678,9 @@
       <c r="A78" s="25" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="27" t="inlineStr">
-        <is>
-          <t>（无）</t>
+      <c r="B78" s="36" t="inlineStr">
+        <is>
+          <t>3316533999026090162</t>
         </is>
       </c>
       <c r="C78" s="36" t="inlineStr">
@@ -9620,7 +9702,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="29" t="n">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="H78" s="34" t="n">
         <v>1673</v>
@@ -9634,7 +9716,7 @@
         </is>
       </c>
       <c r="G80" s="31" t="n">
-        <v>539.9299999999999</v>
+        <v>553.1799999999999</v>
       </c>
       <c r="H80" s="35" t="n">
         <v>103562</v>
@@ -9916,7 +9998,9 @@
     <hyperlink ref="C75" location="'📤销售表'!A75" display="250-0438506-0738236"/>
     <hyperlink ref="B76" location="'📥进货表'!A23" display="3316531515120054152"/>
     <hyperlink ref="C76" location="'📤销售表'!A76" display="249-0515593-2298202"/>
+    <hyperlink ref="B77" location="'📥进货表'!A24" display="3316549190024008960"/>
     <hyperlink ref="C77" location="'📤销售表'!A77" display="503-4832456-8143020"/>
+    <hyperlink ref="B78" location="'📥进货表'!A25" display="3316533999026090162"/>
     <hyperlink ref="C78" location="'📤销售表'!A78" display="249-1477564-5737434"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
